--- a/assets/files/Audit_Workpaper_Template.xlsx
+++ b/assets/files/Audit_Workpaper_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fjmgt-my.sharepoint.com/personal/colby_kellersberger_fjmgt_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2171" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE48414E-45AA-488A-A1AC-6760534244EF}"/>
+  <xr:revisionPtr revIDLastSave="2205" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79C5AC11-02FE-45E7-A30D-AB2C24E98E04}"/>
   <bookViews>
-    <workbookView xWindow="3072" yWindow="1512" windowWidth="29772" windowHeight="22392" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="23232" windowHeight="25296" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Detailed Results 2" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
   <si>
     <t>Tickmark</t>
   </si>
@@ -187,9 +187,6 @@
     <t>Schedule Testing</t>
   </si>
   <si>
-    <t>✘</t>
-  </si>
-  <si>
     <t>Audit Name</t>
   </si>
   <si>
@@ -257,6 +254,15 @@
   </si>
   <si>
     <t>&lt;Title of Data Source tested&gt;</t>
+  </si>
+  <si>
+    <t></t>
+  </si>
+  <si>
+    <t>Attribute tested without exception.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exception noted. </t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1477,7 @@
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1761,23 +1767,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="41" fillId="37" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1793,6 +1785,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1802,12 +1803,39 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1820,24 +1848,6 @@
     <xf numFmtId="0" fontId="2" fillId="34" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1857,18 +1867,17 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="37" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2467,14 +2476,14 @@
   <sheetData>
     <row r="1" spans="2:20" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:20" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -2492,13 +2501,13 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="100"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="102"/>
       <c r="H4" s="59"/>
       <c r="I4" s="59"/>
       <c r="J4" s="13"/>
@@ -2508,13 +2517,13 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="97" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="95"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="105" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="103"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="102"/>
       <c r="H5" s="59"/>
       <c r="I5" s="59"/>
       <c r="J5" s="12"/>
@@ -2524,13 +2533,13 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="95" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="96"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="104"/>
+      <c r="B6" s="103" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="104"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="102"/>
       <c r="H6" s="59"/>
       <c r="I6" s="59"/>
       <c r="J6" s="12"/>
@@ -2564,9 +2573,9 @@
         <v>1</v>
       </c>
       <c r="C10" s="86"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="94"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="99"/>
       <c r="H10" s="24"/>
     </row>
     <row r="11" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2574,9 +2583,9 @@
         <v>2</v>
       </c>
       <c r="C11" s="86"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="94"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="99"/>
       <c r="H11" s="24"/>
     </row>
     <row r="12" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2584,9 +2593,9 @@
         <v>3</v>
       </c>
       <c r="C12" s="86"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="94"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
       <c r="H12" s="24"/>
     </row>
     <row r="13" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2594,9 +2603,9 @@
         <v>4</v>
       </c>
       <c r="C13" s="86"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="94"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="99"/>
       <c r="H13" s="24"/>
     </row>
     <row r="14" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2604,9 +2613,9 @@
         <v>5</v>
       </c>
       <c r="C14" s="86"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="94"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="99"/>
       <c r="H14" s="24"/>
     </row>
     <row r="15" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2630,23 +2639,23 @@
       <c r="B17" s="1"/>
       <c r="F17" s="65"/>
       <c r="G17" s="65"/>
-      <c r="H17" s="101" t="s">
-        <v>58</v>
-      </c>
-      <c r="I17" s="101"/>
-      <c r="J17" s="101"/>
-      <c r="K17" s="101"/>
-      <c r="L17" s="101"/>
+      <c r="H17" s="96" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
     </row>
     <row r="18" spans="2:14" s="31" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="126"/>
-      <c r="D18" s="126"/>
-      <c r="E18" s="126"/>
-      <c r="F18" s="126"/>
-      <c r="G18" s="126"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="92"/>
       <c r="H18" s="85">
         <v>1</v>
       </c>
@@ -2663,7 +2672,7 @@
         <v>5</v>
       </c>
       <c r="M18" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N18" s="18"/>
     </row>
@@ -2677,20 +2686,14 @@
       <c r="F19" s="90"/>
       <c r="G19" s="90"/>
       <c r="H19" s="87" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I19" s="88" t="s">
-        <v>45</v>
-      </c>
-      <c r="J19" s="87" t="s">
-        <v>50</v>
-      </c>
-      <c r="K19" s="87" t="s">
-        <v>50</v>
-      </c>
-      <c r="L19" s="87" t="s">
-        <v>50</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="87"/>
       <c r="M19" s="33"/>
     </row>
     <row r="20" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3109,10 +3112,10 @@
     </row>
     <row r="48" spans="2:13" ht="21" x14ac:dyDescent="0.35">
       <c r="B48" s="45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H48" s="83" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -3123,7 +3126,7 @@
         <v>42</v>
       </c>
       <c r="G49" s="75" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H49" s="85">
         <v>1</v>
@@ -3142,12 +3145,16 @@
       </c>
     </row>
     <row r="50" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B50" s="58"/>
-      <c r="C50" s="92"/>
-      <c r="D50" s="93"/>
-      <c r="E50" s="94"/>
+      <c r="B50" s="127" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" s="97" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" s="98"/>
+      <c r="E50" s="99"/>
       <c r="G50" s="76" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H50" s="79">
         <f>_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G50), IF(_xlpm.x=0, "", _xlpm.x))</f>
@@ -3157,26 +3164,30 @@
         <f t="shared" ref="I50:L51" si="0">_xlfn.LET(_xlpm.x, COUNTIF(I$19:I$43, $G50), IF(_xlpm.x=0, "", _xlpm.x))</f>
         <v/>
       </c>
-      <c r="J50" s="79">
+      <c r="J50" s="79" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K50" s="79">
+        <v/>
+      </c>
+      <c r="K50" s="79" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L50" s="79">
+        <v/>
+      </c>
+      <c r="L50" s="79" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="51" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B51" s="58"/>
-      <c r="C51" s="92"/>
-      <c r="D51" s="93"/>
-      <c r="E51" s="94"/>
+      <c r="B51" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="98"/>
+      <c r="E51" s="99"/>
       <c r="G51" s="77" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H51" s="79" t="str">
         <f>_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G51), IF(_xlpm.x=0, "", _xlpm.x))</f>
@@ -3201,9 +3212,9 @@
     </row>
     <row r="52" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B52" s="58"/>
-      <c r="C52" s="92"/>
-      <c r="D52" s="93"/>
-      <c r="E52" s="94"/>
+      <c r="C52" s="97"/>
+      <c r="D52" s="98"/>
+      <c r="E52" s="99"/>
       <c r="G52" s="78"/>
       <c r="H52" s="79" t="str">
         <f t="shared" ref="H52:L55" si="1">_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G52), IF(_xlpm.x=0, "", _xlpm.x))</f>
@@ -3303,6 +3314,11 @@
     <row r="61" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="H17:L17"/>
@@ -3314,11 +3330,6 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3350,14 +3361,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3377,13 +3388,13 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="105" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
+      <c r="B4" s="106" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="107"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="102"/>
       <c r="H4" s="59"/>
       <c r="I4" s="59"/>
       <c r="J4" s="13"/>
@@ -3394,13 +3405,13 @@
       <c r="U4" s="2"/>
     </row>
     <row r="5" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="105" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="107"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="102"/>
       <c r="H5" s="59"/>
       <c r="I5" s="59"/>
       <c r="J5" s="13"/>
@@ -3426,7 +3437,7 @@
     </row>
     <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.3">
       <c r="B8" s="45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="24"/>
@@ -3449,45 +3460,45 @@
     <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="56"/>
       <c r="C10" s="57"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="94"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="99"/>
       <c r="H10" s="24"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56"/>
       <c r="C11" s="57"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="94"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="99"/>
       <c r="H11" s="24"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56"/>
       <c r="C12" s="57"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="94"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
       <c r="H12" s="24"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56"/>
       <c r="C13" s="57"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="94"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="99"/>
       <c r="H13" s="24"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="56"/>
       <c r="C14" s="57"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="94"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="99"/>
       <c r="H14" s="24"/>
       <c r="N14" s="14"/>
     </row>
@@ -3503,7 +3514,7 @@
     </row>
     <row r="16" spans="2:21" ht="21" x14ac:dyDescent="0.3">
       <c r="B16" s="45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F16" s="53"/>
       <c r="G16" s="24"/>
@@ -3524,25 +3535,25 @@
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="58"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="94"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="99"/>
       <c r="H18" s="24"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="58"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="94"/>
+      <c r="C19" s="97"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="99"/>
       <c r="H19" s="24"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="58"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="99"/>
       <c r="H20" s="24"/>
       <c r="N20" s="14"/>
     </row>
@@ -3586,6 +3597,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D12:F12"/>
@@ -3594,11 +3610,6 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3630,14 +3641,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3657,22 +3668,22 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="106" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="107"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="102"/>
+    </row>
+    <row r="5" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-    </row>
-    <row r="5" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="105" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="102"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
@@ -3683,7 +3694,7 @@
     </row>
     <row r="8" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="24"/>
@@ -3706,45 +3717,45 @@
     <row r="10" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="56"/>
       <c r="C10" s="57"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="94"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="99"/>
       <c r="H10" s="24"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56"/>
       <c r="C11" s="57"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="94"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="99"/>
       <c r="H11" s="24"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56"/>
       <c r="C12" s="57"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="94"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
       <c r="H12" s="24"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B13" s="56"/>
       <c r="C13" s="57"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="94"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="99"/>
       <c r="H13" s="24"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B14" s="56"/>
       <c r="C14" s="57"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="94"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="99"/>
       <c r="H14" s="24"/>
       <c r="N14" s="14"/>
     </row>
@@ -3760,7 +3771,7 @@
     </row>
     <row r="16" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F16" s="53"/>
       <c r="G16" s="24"/>
@@ -3781,25 +3792,25 @@
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="58"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="94"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="99"/>
       <c r="H18" s="24"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B19" s="58"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="94"/>
+      <c r="C19" s="97"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="99"/>
       <c r="H19" s="24"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B20" s="58"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="99"/>
       <c r="H20" s="24"/>
       <c r="N20" s="14"/>
     </row>
@@ -3833,11 +3844,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D12:F12"/>
@@ -3846,6 +3852,11 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3866,64 +3877,64 @@
     <row r="3" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="109"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="110" t="s">
+      <c r="B6" s="117" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="117"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="116"/>
+    </row>
+    <row r="7" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="110"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="109"/>
-    </row>
-    <row r="7" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="95" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="104"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="102"/>
     </row>
     <row r="9" spans="2:10" ht="21" x14ac:dyDescent="0.3">
       <c r="B9" s="60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="18" x14ac:dyDescent="0.35">
       <c r="B10" s="61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="114"/>
-      <c r="C11" s="115"/>
-      <c r="D11" s="115"/>
-      <c r="E11" s="115"/>
-      <c r="F11" s="115"/>
-      <c r="G11" s="115"/>
-      <c r="H11" s="115"/>
-      <c r="I11" s="115"/>
-      <c r="J11" s="116"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="14"/>
@@ -3933,35 +3944,35 @@
     </row>
     <row r="13" spans="2:10" ht="18" x14ac:dyDescent="0.35">
       <c r="B13" s="61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="114"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="116"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="112"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="112"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="113"/>
     </row>
     <row r="16" spans="2:10" ht="18" x14ac:dyDescent="0.35">
       <c r="B16" s="61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="116"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="112"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="113"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="54"/>
@@ -3971,22 +3982,22 @@
     </row>
     <row r="19" spans="2:10" ht="18" x14ac:dyDescent="0.3">
       <c r="B19" s="62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C19" s="54"/>
       <c r="D19" s="54"/>
       <c r="E19" s="54"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="114"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="115"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="116"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="112"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="112"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="112"/>
+      <c r="J20" s="113"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="14"/>
@@ -3996,22 +4007,22 @@
     </row>
     <row r="22" spans="2:10" ht="18" x14ac:dyDescent="0.3">
       <c r="B22" s="63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="114"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="116"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="112"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="113"/>
     </row>
     <row r="25" spans="2:10" ht="21" x14ac:dyDescent="0.3">
       <c r="B25" s="45" t="s">
@@ -4028,41 +4039,47 @@
     </row>
     <row r="27" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B27" s="64"/>
-      <c r="C27" s="111"/>
-      <c r="D27" s="112"/>
-      <c r="E27" s="112"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="113"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="109"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="109"/>
+      <c r="G27" s="109"/>
+      <c r="H27" s="110"/>
     </row>
     <row r="28" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B28" s="64"/>
-      <c r="C28" s="111"/>
-      <c r="D28" s="112"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="112"/>
-      <c r="G28" s="112"/>
-      <c r="H28" s="113"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="109"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="109"/>
+      <c r="H28" s="110"/>
     </row>
     <row r="29" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B29" s="64"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="94"/>
+      <c r="C29" s="97"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="99"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="8"/>
     </row>
     <row r="31" spans="2:10" ht="21" x14ac:dyDescent="0.3">
       <c r="B31" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:J7"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="B11:J11"/>
@@ -4071,12 +4088,6 @@
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="C27:H27"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4109,14 +4120,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -4136,12 +4147,12 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="120" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="121"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="123"/>
+      <c r="B4" s="121" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="122"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="124"/>
       <c r="G4" s="65"/>
       <c r="H4" s="59"/>
       <c r="I4" s="59"/>
@@ -4172,21 +4183,21 @@
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="54"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="119"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="120"/>
       <c r="G7" s="65"/>
     </row>
     <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.3">
       <c r="B9" s="45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" s="51"/>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C10" s="117"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="119"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="120"/>
       <c r="G10" s="65"/>
     </row>
     <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.3">
@@ -4195,36 +4206,36 @@
       </c>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="119"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="120"/>
       <c r="G13" s="65"/>
     </row>
     <row r="15" spans="2:21" ht="21" x14ac:dyDescent="0.3">
       <c r="B15" s="45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="119"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="120"/>
       <c r="G16" s="65"/>
     </row>
     <row r="18" spans="2:5" ht="21" x14ac:dyDescent="0.3">
       <c r="B18" s="45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="67" t="s">
+      <c r="E19" s="68" t="s">
         <v>54</v>
-      </c>
-      <c r="E19" s="68" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
@@ -4320,10 +4331,10 @@
       <c r="B3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="124" t="s">
+      <c r="C3" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="124"/>
+      <c r="D3" s="126"/>
       <c r="F3" s="125" t="s">
         <v>5</v>
       </c>
@@ -4334,10 +4345,10 @@
       <c r="B4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="124" t="s">
+      <c r="C4" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="124"/>
+      <c r="D4" s="126"/>
       <c r="F4" s="36" t="s">
         <v>8</v>
       </c>
@@ -4347,10 +4358,10 @@
       <c r="B5" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="124" t="s">
+      <c r="C5" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="124"/>
+      <c r="D5" s="126"/>
       <c r="F5" s="36" t="s">
         <v>11</v>
       </c>
@@ -4360,10 +4371,10 @@
       <c r="B6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="124" t="s">
+      <c r="C6" s="126" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="124"/>
+      <c r="D6" s="126"/>
       <c r="F6" s="37" t="s">
         <v>14</v>
       </c>
@@ -4373,10 +4384,10 @@
       <c r="B7" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="124" t="s">
+      <c r="C7" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="124"/>
+      <c r="D7" s="126"/>
       <c r="F7" s="35" t="s">
         <v>17</v>
       </c>
@@ -4386,46 +4397,46 @@
       <c r="B8" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="124" t="s">
+      <c r="C8" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="124"/>
+      <c r="D8" s="126"/>
     </row>
     <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="124" t="s">
+      <c r="C9" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="124"/>
+      <c r="D9" s="126"/>
     </row>
     <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="124" t="s">
+      <c r="C10" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="124"/>
+      <c r="D10" s="126"/>
     </row>
     <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="124" t="s">
+      <c r="C11" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="124"/>
+      <c r="D11" s="126"/>
     </row>
     <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="124" t="s">
+      <c r="C12" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="124"/>
+      <c r="D12" s="126"/>
     </row>
     <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="42"/>
@@ -4435,32 +4446,27 @@
       <c r="B14" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="124" t="s">
+      <c r="C14" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="124"/>
+      <c r="D14" s="126"/>
     </row>
     <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="41"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="124"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
     </row>
     <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="124" t="s">
+      <c r="C16" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="124"/>
+      <c r="D16" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
@@ -4470,6 +4476,11 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4504,15 +4515,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F6BF0C1AE5C4B149A9D2AD89D2837366" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="26a77736960804fb0d99dc8dd7184fdb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="c596204b-3c01-4828-83dd-c39c80911371" xmlns:ns3="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94048c9244edca77c34ed05855514cda" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4784,6 +4786,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
   <ds:schemaRefs>
@@ -4803,14 +4814,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24C080E9-4052-4FFB-9585-503A5ED8519B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4828,4 +4831,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assets/files/Audit_Workpaper_Template.xlsx
+++ b/assets/files/Audit_Workpaper_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fjmgt-my.sharepoint.com/personal/colby_kellersberger_fjmgt_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2205" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79C5AC11-02FE-45E7-A30D-AB2C24E98E04}"/>
+  <xr:revisionPtr revIDLastSave="2227" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2A6D634-C859-4016-B394-287DDA3F8373}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="23232" windowHeight="25296" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="1116" windowWidth="29772" windowHeight="22392" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Detailed Results 2" sheetId="5" r:id="rId1"/>
@@ -269,7 +269,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="56" x14ac:knownFonts="1">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -683,6 +683,28 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="38">
@@ -1477,7 +1499,7 @@
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1734,9 +1756,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1767,9 +1786,26 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="37" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1785,15 +1821,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1803,21 +1830,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1836,18 +1866,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1867,17 +1885,27 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="37" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2476,14 +2504,14 @@
   <sheetData>
     <row r="1" spans="2:20" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:20" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -2501,13 +2529,13 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
       <c r="H4" s="59"/>
       <c r="I4" s="59"/>
       <c r="J4" s="13"/>
@@ -2517,13 +2545,13 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="102"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="104"/>
       <c r="H5" s="59"/>
       <c r="I5" s="59"/>
       <c r="J5" s="12"/>
@@ -2533,13 +2561,13 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="103" t="s">
+      <c r="B6" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="104"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="102"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="104"/>
       <c r="H6" s="59"/>
       <c r="I6" s="59"/>
       <c r="J6" s="12"/>
@@ -2549,14 +2577,14 @@
       <c r="T6" s="2"/>
     </row>
     <row r="8" spans="2:20" ht="21" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="126" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="24"/>
     </row>
     <row r="9" spans="2:20" ht="21" x14ac:dyDescent="0.3">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="127" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="47" t="s">
@@ -2572,58 +2600,58 @@
       <c r="B10" s="56">
         <v>1</v>
       </c>
-      <c r="C10" s="86"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="99"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="94"/>
       <c r="H10" s="24"/>
     </row>
     <row r="11" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56">
         <v>2</v>
       </c>
-      <c r="C11" s="86"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="99"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="94"/>
       <c r="H11" s="24"/>
     </row>
     <row r="12" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56">
         <v>3</v>
       </c>
-      <c r="C12" s="86"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="99"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="94"/>
       <c r="H12" s="24"/>
     </row>
     <row r="13" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56">
         <v>4</v>
       </c>
-      <c r="C13" s="86"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="99"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="94"/>
       <c r="H13" s="24"/>
     </row>
     <row r="14" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="56">
         <v>5</v>
       </c>
-      <c r="C14" s="86"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="99"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="94"/>
       <c r="H14" s="24"/>
     </row>
     <row r="15" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="56"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
       <c r="H15" s="24"/>
     </row>
     <row r="16" spans="2:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2639,36 +2667,36 @@
       <c r="B17" s="1"/>
       <c r="F17" s="65"/>
       <c r="G17" s="65"/>
-      <c r="H17" s="96" t="s">
+      <c r="H17" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
+      <c r="I17" s="101"/>
+      <c r="J17" s="101"/>
+      <c r="K17" s="101"/>
+      <c r="L17" s="101"/>
     </row>
     <row r="18" spans="2:14" s="31" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="92"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="92"/>
-      <c r="H18" s="85">
+      <c r="C18" s="129"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="84">
         <v>1</v>
       </c>
-      <c r="I18" s="85">
+      <c r="I18" s="84">
         <v>2</v>
       </c>
-      <c r="J18" s="85">
+      <c r="J18" s="84">
         <v>3</v>
       </c>
-      <c r="K18" s="85">
+      <c r="K18" s="84">
         <v>4</v>
       </c>
-      <c r="L18" s="85">
+      <c r="L18" s="84">
         <v>5</v>
       </c>
       <c r="M18" s="17" t="s">
@@ -2680,32 +2708,32 @@
       <c r="B19" s="25">
         <v>1</v>
       </c>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="87" t="s">
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="I19" s="88" t="s">
+      <c r="I19" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="J19" s="87"/>
-      <c r="K19" s="87"/>
-      <c r="L19" s="87"/>
+      <c r="J19" s="86"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="86"/>
       <c r="M19" s="33"/>
     </row>
     <row r="20" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="25">
         <v>2</v>
       </c>
-      <c r="C20" s="91"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="89"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="88"/>
       <c r="I20" s="21"/>
       <c r="J20" s="22"/>
       <c r="K20" s="23"/>
@@ -2716,12 +2744,12 @@
       <c r="B21" s="25">
         <v>3</v>
       </c>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="91"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="89"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="88"/>
       <c r="I21" s="21"/>
       <c r="J21" s="22"/>
       <c r="K21" s="23"/>
@@ -2732,12 +2760,12 @@
       <c r="B22" s="25">
         <v>4</v>
       </c>
-      <c r="C22" s="91"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="89"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="88"/>
       <c r="I22" s="21"/>
       <c r="J22" s="22"/>
       <c r="K22" s="23"/>
@@ -2748,12 +2776,12 @@
       <c r="B23" s="25">
         <v>5</v>
       </c>
-      <c r="C23" s="91"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="91"/>
-      <c r="H23" s="89"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="90"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="88"/>
       <c r="I23" s="21"/>
       <c r="J23" s="22"/>
       <c r="K23" s="23"/>
@@ -2764,12 +2792,12 @@
       <c r="B24" s="25">
         <v>6</v>
       </c>
-      <c r="C24" s="91"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="89"/>
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="88"/>
       <c r="I24" s="21"/>
       <c r="J24" s="22"/>
       <c r="K24" s="23"/>
@@ -2780,12 +2808,12 @@
       <c r="B25" s="25">
         <v>7</v>
       </c>
-      <c r="C25" s="91"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="91"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="91"/>
-      <c r="H25" s="89"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="90"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="88"/>
       <c r="I25" s="21"/>
       <c r="J25" s="22"/>
       <c r="K25" s="23"/>
@@ -2796,12 +2824,12 @@
       <c r="B26" s="25">
         <v>8</v>
       </c>
-      <c r="C26" s="91"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="91"/>
-      <c r="H26" s="89"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="88"/>
       <c r="I26" s="21"/>
       <c r="J26" s="22"/>
       <c r="K26" s="23"/>
@@ -2812,12 +2840,12 @@
       <c r="B27" s="25">
         <v>9</v>
       </c>
-      <c r="C27" s="91"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="91"/>
-      <c r="H27" s="89"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="90"/>
+      <c r="F27" s="90"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="88"/>
       <c r="I27" s="21"/>
       <c r="J27" s="22"/>
       <c r="K27" s="23"/>
@@ -2828,12 +2856,12 @@
       <c r="B28" s="25">
         <v>10</v>
       </c>
-      <c r="C28" s="91"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="91"/>
-      <c r="H28" s="89"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="88"/>
       <c r="I28" s="21"/>
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
@@ -2844,12 +2872,12 @@
       <c r="B29" s="25">
         <v>11</v>
       </c>
-      <c r="C29" s="91"/>
-      <c r="D29" s="91"/>
-      <c r="E29" s="91"/>
-      <c r="F29" s="91"/>
-      <c r="G29" s="91"/>
-      <c r="H29" s="89"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90"/>
+      <c r="F29" s="90"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="88"/>
       <c r="I29" s="21"/>
       <c r="J29" s="22"/>
       <c r="K29" s="23"/>
@@ -2860,12 +2888,12 @@
       <c r="B30" s="25">
         <v>12</v>
       </c>
-      <c r="C30" s="91"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="91"/>
-      <c r="F30" s="91"/>
-      <c r="G30" s="91"/>
-      <c r="H30" s="89"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="90"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="88"/>
       <c r="I30" s="21"/>
       <c r="J30" s="22"/>
       <c r="K30" s="23"/>
@@ -2876,12 +2904,12 @@
       <c r="B31" s="25">
         <v>13</v>
       </c>
-      <c r="C31" s="91"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="91"/>
-      <c r="F31" s="91"/>
-      <c r="G31" s="91"/>
-      <c r="H31" s="89"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="90"/>
+      <c r="F31" s="90"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="88"/>
       <c r="I31" s="21"/>
       <c r="J31" s="22"/>
       <c r="K31" s="23"/>
@@ -2892,12 +2920,12 @@
       <c r="B32" s="25">
         <v>14</v>
       </c>
-      <c r="C32" s="91"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="91"/>
-      <c r="F32" s="91"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="89"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="90"/>
+      <c r="E32" s="90"/>
+      <c r="F32" s="90"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="88"/>
       <c r="I32" s="21"/>
       <c r="J32" s="22"/>
       <c r="K32" s="23"/>
@@ -2908,12 +2936,12 @@
       <c r="B33" s="25">
         <v>15</v>
       </c>
-      <c r="C33" s="91"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
-      <c r="F33" s="91"/>
-      <c r="G33" s="91"/>
-      <c r="H33" s="89"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="90"/>
+      <c r="F33" s="90"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="88"/>
       <c r="I33" s="21"/>
       <c r="J33" s="22"/>
       <c r="K33" s="23"/>
@@ -2924,12 +2952,12 @@
       <c r="B34" s="25">
         <v>16</v>
       </c>
-      <c r="C34" s="91"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="91"/>
-      <c r="G34" s="91"/>
-      <c r="H34" s="89"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="90"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="88"/>
       <c r="I34" s="21"/>
       <c r="J34" s="22"/>
       <c r="K34" s="23"/>
@@ -2940,12 +2968,12 @@
       <c r="B35" s="25">
         <v>17</v>
       </c>
-      <c r="C35" s="91"/>
-      <c r="D35" s="91"/>
-      <c r="E35" s="91"/>
-      <c r="F35" s="91"/>
-      <c r="G35" s="91"/>
-      <c r="H35" s="89"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="90"/>
+      <c r="F35" s="90"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="88"/>
       <c r="I35" s="21"/>
       <c r="J35" s="22"/>
       <c r="K35" s="23"/>
@@ -2956,12 +2984,12 @@
       <c r="B36" s="25">
         <v>18</v>
       </c>
-      <c r="C36" s="91"/>
-      <c r="D36" s="91"/>
-      <c r="E36" s="91"/>
-      <c r="F36" s="91"/>
-      <c r="G36" s="91"/>
-      <c r="H36" s="89"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="90"/>
+      <c r="F36" s="90"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="88"/>
       <c r="I36" s="21"/>
       <c r="J36" s="22"/>
       <c r="K36" s="23"/>
@@ -2972,12 +3000,12 @@
       <c r="B37" s="25">
         <v>19</v>
       </c>
-      <c r="C37" s="91"/>
-      <c r="D37" s="91"/>
-      <c r="E37" s="91"/>
-      <c r="F37" s="91"/>
-      <c r="G37" s="91"/>
-      <c r="H37" s="89"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="90"/>
+      <c r="G37" s="90"/>
+      <c r="H37" s="88"/>
       <c r="I37" s="21"/>
       <c r="J37" s="22"/>
       <c r="K37" s="23"/>
@@ -2988,12 +3016,12 @@
       <c r="B38" s="25">
         <v>20</v>
       </c>
-      <c r="C38" s="91"/>
-      <c r="D38" s="91"/>
-      <c r="E38" s="91"/>
-      <c r="F38" s="91"/>
-      <c r="G38" s="91"/>
-      <c r="H38" s="89"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="90"/>
+      <c r="E38" s="90"/>
+      <c r="F38" s="90"/>
+      <c r="G38" s="90"/>
+      <c r="H38" s="88"/>
       <c r="I38" s="21"/>
       <c r="J38" s="22"/>
       <c r="K38" s="23"/>
@@ -3004,12 +3032,12 @@
       <c r="B39" s="25">
         <v>21</v>
       </c>
-      <c r="C39" s="91"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="91"/>
-      <c r="F39" s="91"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="89"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="90"/>
+      <c r="E39" s="90"/>
+      <c r="F39" s="90"/>
+      <c r="G39" s="90"/>
+      <c r="H39" s="88"/>
       <c r="I39" s="21"/>
       <c r="J39" s="22"/>
       <c r="K39" s="23"/>
@@ -3020,12 +3048,12 @@
       <c r="B40" s="25">
         <v>22</v>
       </c>
-      <c r="C40" s="91"/>
-      <c r="D40" s="91"/>
-      <c r="E40" s="91"/>
-      <c r="F40" s="91"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="89"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="90"/>
+      <c r="H40" s="88"/>
       <c r="I40" s="21"/>
       <c r="J40" s="22"/>
       <c r="K40" s="23"/>
@@ -3036,12 +3064,12 @@
       <c r="B41" s="25">
         <v>23</v>
       </c>
-      <c r="C41" s="91"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="89"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="H41" s="88"/>
       <c r="I41" s="21"/>
       <c r="J41" s="22"/>
       <c r="K41" s="23"/>
@@ -3052,12 +3080,12 @@
       <c r="B42" s="25">
         <v>24</v>
       </c>
-      <c r="C42" s="91"/>
-      <c r="D42" s="91"/>
-      <c r="E42" s="91"/>
-      <c r="F42" s="91"/>
-      <c r="G42" s="91"/>
-      <c r="H42" s="89"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="90"/>
+      <c r="F42" s="90"/>
+      <c r="G42" s="90"/>
+      <c r="H42" s="88"/>
       <c r="I42" s="21"/>
       <c r="J42" s="22"/>
       <c r="K42" s="23"/>
@@ -3068,12 +3096,12 @@
       <c r="B43" s="25">
         <v>25</v>
       </c>
-      <c r="C43" s="91"/>
-      <c r="D43" s="91"/>
-      <c r="E43" s="91"/>
-      <c r="F43" s="91"/>
-      <c r="G43" s="91"/>
-      <c r="H43" s="89"/>
+      <c r="C43" s="90"/>
+      <c r="D43" s="90"/>
+      <c r="E43" s="90"/>
+      <c r="F43" s="90"/>
+      <c r="G43" s="90"/>
+      <c r="H43" s="88"/>
       <c r="I43" s="21"/>
       <c r="J43" s="22"/>
       <c r="K43" s="23"/>
@@ -3110,16 +3138,17 @@
     <row r="47" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C47" s="55"/>
     </row>
-    <row r="48" spans="2:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="B48" s="45" t="s">
+    <row r="48" spans="2:13" ht="21" x14ac:dyDescent="0.4">
+      <c r="B48" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="H48" s="83" t="s">
+      <c r="G48" s="65"/>
+      <c r="H48" s="128" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="49" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B49" s="49" t="s">
+      <c r="B49" s="127" t="s">
         <v>35</v>
       </c>
       <c r="C49" s="50" t="s">
@@ -3128,31 +3157,31 @@
       <c r="G49" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H49" s="85">
+      <c r="H49" s="84">
         <v>1</v>
       </c>
-      <c r="I49" s="85">
+      <c r="I49" s="84">
         <v>2</v>
       </c>
-      <c r="J49" s="85">
+      <c r="J49" s="84">
         <v>3</v>
       </c>
-      <c r="K49" s="85">
+      <c r="K49" s="84">
         <v>4</v>
       </c>
-      <c r="L49" s="85">
+      <c r="L49" s="84">
         <v>5</v>
       </c>
     </row>
     <row r="50" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B50" s="127" t="s">
+      <c r="B50" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="97" t="s">
+      <c r="C50" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="D50" s="98"/>
-      <c r="E50" s="99"/>
+      <c r="D50" s="93"/>
+      <c r="E50" s="94"/>
       <c r="G50" s="76" t="s">
         <v>49</v>
       </c>
@@ -3181,11 +3210,11 @@
       <c r="B51" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="C51" s="97" t="s">
+      <c r="C51" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="D51" s="98"/>
-      <c r="E51" s="99"/>
+      <c r="D51" s="93"/>
+      <c r="E51" s="94"/>
       <c r="G51" s="77" t="s">
         <v>68</v>
       </c>
@@ -3212,9 +3241,9 @@
     </row>
     <row r="52" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B52" s="58"/>
-      <c r="C52" s="97"/>
-      <c r="D52" s="98"/>
-      <c r="E52" s="99"/>
+      <c r="C52" s="92"/>
+      <c r="D52" s="93"/>
+      <c r="E52" s="94"/>
       <c r="G52" s="78"/>
       <c r="H52" s="79" t="str">
         <f t="shared" ref="H52:L55" si="1">_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G52), IF(_xlpm.x=0, "", _xlpm.x))</f>
@@ -3314,11 +3343,6 @@
     <row r="61" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="H17:L17"/>
@@ -3330,6 +3354,11 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3361,14 +3390,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3388,13 +3417,13 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
       <c r="H4" s="59"/>
       <c r="I4" s="59"/>
       <c r="J4" s="13"/>
@@ -3405,13 +3434,13 @@
       <c r="U4" s="2"/>
     </row>
     <row r="5" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="106" t="s">
+      <c r="B5" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="102"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="104"/>
       <c r="H5" s="59"/>
       <c r="I5" s="59"/>
       <c r="J5" s="13"/>
@@ -3460,45 +3489,45 @@
     <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="56"/>
       <c r="C10" s="57"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="99"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="94"/>
       <c r="H10" s="24"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56"/>
       <c r="C11" s="57"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="99"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="94"/>
       <c r="H11" s="24"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56"/>
       <c r="C12" s="57"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="99"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="94"/>
       <c r="H12" s="24"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56"/>
       <c r="C13" s="57"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="99"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="94"/>
       <c r="H13" s="24"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="56"/>
       <c r="C14" s="57"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="99"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="94"/>
       <c r="H14" s="24"/>
       <c r="N14" s="14"/>
     </row>
@@ -3535,25 +3564,25 @@
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="58"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="99"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="94"/>
       <c r="H18" s="24"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="58"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="99"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="94"/>
       <c r="H19" s="24"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="58"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="99"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="94"/>
       <c r="H20" s="24"/>
       <c r="N20" s="14"/>
     </row>
@@ -3597,11 +3626,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:F5"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D12:F12"/>
@@ -3610,6 +3634,11 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3641,14 +3670,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3668,22 +3697,22 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
     </row>
     <row r="5" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="106" t="s">
+      <c r="B5" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="102"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="104"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
@@ -3717,45 +3746,45 @@
     <row r="10" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="56"/>
       <c r="C10" s="57"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="99"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="94"/>
       <c r="H10" s="24"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56"/>
       <c r="C11" s="57"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="99"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="94"/>
       <c r="H11" s="24"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56"/>
       <c r="C12" s="57"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="99"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="94"/>
       <c r="H12" s="24"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B13" s="56"/>
       <c r="C13" s="57"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="99"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="94"/>
       <c r="H13" s="24"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B14" s="56"/>
       <c r="C14" s="57"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="99"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="94"/>
       <c r="H14" s="24"/>
       <c r="N14" s="14"/>
     </row>
@@ -3792,25 +3821,25 @@
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="58"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="99"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="94"/>
       <c r="H18" s="24"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B19" s="58"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="99"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="94"/>
       <c r="H19" s="24"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B20" s="58"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="99"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="94"/>
       <c r="H20" s="24"/>
       <c r="N20" s="14"/>
     </row>
@@ -3844,6 +3873,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D12:F12"/>
@@ -3852,11 +3886,6 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3877,43 +3906,43 @@
     <row r="3" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="106" t="s">
+      <c r="B5" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="115"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="116"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="109"/>
     </row>
     <row r="6" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="117" t="s">
+      <c r="B6" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="114"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="116"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="109"/>
     </row>
     <row r="7" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="102"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="104"/>
     </row>
     <row r="9" spans="2:10" ht="21" x14ac:dyDescent="0.3">
       <c r="B9" s="60" t="s">
@@ -3926,15 +3955,15 @@
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="111"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="112"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="113"/>
+      <c r="B11" s="114"/>
+      <c r="C11" s="115"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="116"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="14"/>
@@ -3948,15 +3977,15 @@
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="111"/>
-      <c r="C14" s="112"/>
-      <c r="D14" s="112"/>
-      <c r="E14" s="112"/>
-      <c r="F14" s="112"/>
-      <c r="G14" s="112"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="112"/>
-      <c r="J14" s="113"/>
+      <c r="B14" s="114"/>
+      <c r="C14" s="115"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="116"/>
     </row>
     <row r="16" spans="2:10" ht="18" x14ac:dyDescent="0.35">
       <c r="B16" s="61" t="s">
@@ -3964,15 +3993,15 @@
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="111"/>
-      <c r="C17" s="112"/>
-      <c r="D17" s="112"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="112"/>
-      <c r="G17" s="112"/>
-      <c r="H17" s="112"/>
-      <c r="I17" s="112"/>
-      <c r="J17" s="113"/>
+      <c r="B17" s="114"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="116"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="54"/>
@@ -3989,15 +4018,15 @@
       <c r="E19" s="54"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="111"/>
-      <c r="C20" s="112"/>
-      <c r="D20" s="112"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="112"/>
-      <c r="G20" s="112"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="112"/>
-      <c r="J20" s="113"/>
+      <c r="B20" s="114"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="115"/>
+      <c r="J20" s="116"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="14"/>
@@ -4014,15 +4043,15 @@
       <c r="E22" s="14"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="111"/>
-      <c r="C23" s="112"/>
-      <c r="D23" s="112"/>
-      <c r="E23" s="112"/>
-      <c r="F23" s="112"/>
-      <c r="G23" s="112"/>
-      <c r="H23" s="112"/>
-      <c r="I23" s="112"/>
-      <c r="J23" s="113"/>
+      <c r="B23" s="114"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="115"/>
+      <c r="G23" s="115"/>
+      <c r="H23" s="115"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="116"/>
     </row>
     <row r="25" spans="2:10" ht="21" x14ac:dyDescent="0.3">
       <c r="B25" s="45" t="s">
@@ -4039,30 +4068,30 @@
     </row>
     <row r="27" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B27" s="64"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="109"/>
-      <c r="E27" s="109"/>
-      <c r="F27" s="109"/>
-      <c r="G27" s="109"/>
-      <c r="H27" s="110"/>
+      <c r="C27" s="111"/>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="113"/>
     </row>
     <row r="28" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B28" s="64"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="109"/>
-      <c r="E28" s="109"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="109"/>
-      <c r="H28" s="110"/>
+      <c r="C28" s="111"/>
+      <c r="D28" s="112"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="112"/>
+      <c r="H28" s="113"/>
     </row>
     <row r="29" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B29" s="64"/>
-      <c r="C29" s="97"/>
-      <c r="D29" s="98"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="98"/>
-      <c r="G29" s="98"/>
-      <c r="H29" s="99"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="93"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="93"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="94"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="8"/>
@@ -4074,12 +4103,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:J7"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="B11:J11"/>
@@ -4088,6 +4111,12 @@
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="C27:H27"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4120,14 +4149,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -4147,12 +4176,12 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="120" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="122"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="124"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="123"/>
       <c r="G4" s="65"/>
       <c r="H4" s="59"/>
       <c r="I4" s="59"/>
@@ -4183,9 +4212,9 @@
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="54"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="119"/>
-      <c r="E7" s="120"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="119"/>
       <c r="G7" s="65"/>
     </row>
     <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.3">
@@ -4195,9 +4224,9 @@
       <c r="C9" s="51"/>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C10" s="118"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="120"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="119"/>
       <c r="G10" s="65"/>
     </row>
     <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.3">
@@ -4206,9 +4235,9 @@
       </c>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C13" s="118"/>
-      <c r="D13" s="119"/>
-      <c r="E13" s="120"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="119"/>
       <c r="G13" s="65"/>
     </row>
     <row r="15" spans="2:21" ht="21" x14ac:dyDescent="0.3">
@@ -4217,9 +4246,9 @@
       </c>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C16" s="118"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="120"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="119"/>
       <c r="G16" s="65"/>
     </row>
     <row r="18" spans="2:5" ht="21" x14ac:dyDescent="0.3">
@@ -4331,10 +4360,10 @@
       <c r="B3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="126" t="s">
+      <c r="C3" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="126"/>
+      <c r="D3" s="124"/>
       <c r="F3" s="125" t="s">
         <v>5</v>
       </c>
@@ -4345,10 +4374,10 @@
       <c r="B4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="126" t="s">
+      <c r="C4" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="126"/>
+      <c r="D4" s="124"/>
       <c r="F4" s="36" t="s">
         <v>8</v>
       </c>
@@ -4358,10 +4387,10 @@
       <c r="B5" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="126" t="s">
+      <c r="C5" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="126"/>
+      <c r="D5" s="124"/>
       <c r="F5" s="36" t="s">
         <v>11</v>
       </c>
@@ -4371,10 +4400,10 @@
       <c r="B6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="126" t="s">
+      <c r="C6" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="126"/>
+      <c r="D6" s="124"/>
       <c r="F6" s="37" t="s">
         <v>14</v>
       </c>
@@ -4384,10 +4413,10 @@
       <c r="B7" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="126" t="s">
+      <c r="C7" s="124" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="126"/>
+      <c r="D7" s="124"/>
       <c r="F7" s="35" t="s">
         <v>17</v>
       </c>
@@ -4397,46 +4426,46 @@
       <c r="B8" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="126" t="s">
+      <c r="C8" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="126"/>
+      <c r="D8" s="124"/>
     </row>
     <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="126" t="s">
+      <c r="C9" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="126"/>
+      <c r="D9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="126" t="s">
+      <c r="C10" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="126"/>
+      <c r="D10" s="124"/>
     </row>
     <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="126" t="s">
+      <c r="C11" s="124" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="126"/>
+      <c r="D11" s="124"/>
     </row>
     <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="126" t="s">
+      <c r="C12" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="126"/>
+      <c r="D12" s="124"/>
     </row>
     <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="42"/>
@@ -4446,27 +4475,32 @@
       <c r="B14" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="126" t="s">
+      <c r="C14" s="124" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="126"/>
+      <c r="D14" s="124"/>
     </row>
     <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="41"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="126" t="s">
+      <c r="C16" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="126"/>
+      <c r="D16" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
@@ -4476,42 +4510,18 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
-    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4787,28 +4797,37 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
+    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4834,9 +4853,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/assets/files/Audit_Workpaper_Template.xlsx
+++ b/assets/files/Audit_Workpaper_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fjmgt-my.sharepoint.com/personal/colby_kellersberger_fjmgt_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2227" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2A6D634-C859-4016-B394-287DDA3F8373}"/>
+  <xr:revisionPtr revIDLastSave="2246" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D0302E5-3476-4AEB-B65B-57DC46F5EE9F}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="1116" windowWidth="29772" windowHeight="22392" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -269,7 +269,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="60" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,14 +486,6 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FFF68925"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF15488B"/>
       <name val="Calibri"/>
@@ -588,13 +580,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="16"/>
-      <color rgb="FFFF6600"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -648,8 +633,67 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
       <sz val="16"/>
-      <color rgb="FFF68925"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -657,51 +701,14 @@
       <b/>
       <i/>
       <sz val="14"/>
-      <color rgb="FFF68925"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="16"/>
-      <color theme="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="16"/>
-      <color theme="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1499,7 +1506,7 @@
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1546,24 +1553,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1579,11 +1582,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -1606,7 +1609,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -1615,7 +1618,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1628,46 +1631,37 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="37" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1676,29 +1670,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1731,20 +1715,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1756,21 +1740,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="34" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="40" fillId="34" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1786,26 +1770,21 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="37" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1817,10 +1796,19 @@
     <xf numFmtId="0" fontId="2" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="34" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="50" fillId="34" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1830,12 +1818,39 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1848,24 +1863,6 @@
     <xf numFmtId="0" fontId="2" fillId="34" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1881,32 +1878,43 @@
     <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="37" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
@@ -2504,14 +2512,14 @@
   <sheetData>
     <row r="1" spans="2:20" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:20" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -2529,15 +2537,15 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="89" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="100"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="97"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
       <c r="R4" s="2"/>
@@ -2545,15 +2553,15 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="95"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="97"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
       <c r="R5" s="2"/>
@@ -2561,15 +2569,15 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="95" t="s">
+      <c r="B6" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="96"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="104"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="97"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
       <c r="R6" s="2"/>
@@ -2577,550 +2585,550 @@
       <c r="T6" s="2"/>
     </row>
     <row r="8" spans="2:20" ht="21" x14ac:dyDescent="0.3">
-      <c r="B8" s="126" t="s">
+      <c r="B8" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="2:20" ht="21" x14ac:dyDescent="0.3">
-      <c r="B9" s="127" t="s">
+      <c r="B9" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="56">
+      <c r="B10" s="52">
         <v>1</v>
       </c>
-      <c r="C10" s="85"/>
+      <c r="C10" s="77"/>
       <c r="D10" s="92"/>
       <c r="E10" s="93"/>
       <c r="F10" s="94"/>
-      <c r="H10" s="24"/>
+      <c r="H10" s="23"/>
     </row>
     <row r="11" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="56">
+      <c r="B11" s="52">
         <v>2</v>
       </c>
-      <c r="C11" s="85"/>
+      <c r="C11" s="77"/>
       <c r="D11" s="92"/>
       <c r="E11" s="93"/>
       <c r="F11" s="94"/>
-      <c r="H11" s="24"/>
+      <c r="H11" s="23"/>
     </row>
     <row r="12" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="56">
+      <c r="B12" s="52">
         <v>3</v>
       </c>
-      <c r="C12" s="85"/>
+      <c r="C12" s="77"/>
       <c r="D12" s="92"/>
       <c r="E12" s="93"/>
       <c r="F12" s="94"/>
-      <c r="H12" s="24"/>
+      <c r="H12" s="23"/>
     </row>
     <row r="13" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="56">
+      <c r="B13" s="52">
         <v>4</v>
       </c>
-      <c r="C13" s="85"/>
+      <c r="C13" s="77"/>
       <c r="D13" s="92"/>
       <c r="E13" s="93"/>
       <c r="F13" s="94"/>
-      <c r="H13" s="24"/>
+      <c r="H13" s="23"/>
     </row>
     <row r="14" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="56">
+      <c r="B14" s="52">
         <v>5</v>
       </c>
-      <c r="C14" s="85"/>
+      <c r="C14" s="77"/>
       <c r="D14" s="92"/>
       <c r="E14" s="93"/>
       <c r="F14" s="94"/>
-      <c r="H14" s="24"/>
+      <c r="H14" s="23"/>
     </row>
     <row r="15" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="56"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="H15" s="24"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" spans="2:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="48"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
     </row>
     <row r="17" spans="2:14" ht="23.4" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="101" t="s">
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="91" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="101"/>
-      <c r="J17" s="101"/>
-      <c r="K17" s="101"/>
-      <c r="L17" s="101"/>
-    </row>
-    <row r="18" spans="2:14" s="31" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="16" t="s">
+      <c r="I17" s="91"/>
+      <c r="J17" s="91"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="91"/>
+    </row>
+    <row r="18" spans="2:14" s="30" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="129"/>
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="84">
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="76">
         <v>1</v>
       </c>
-      <c r="I18" s="84">
+      <c r="I18" s="76">
         <v>2</v>
       </c>
-      <c r="J18" s="84">
+      <c r="J18" s="76">
         <v>3</v>
       </c>
-      <c r="K18" s="84">
+      <c r="K18" s="76">
         <v>4</v>
       </c>
-      <c r="L18" s="84">
+      <c r="L18" s="76">
         <v>5</v>
       </c>
-      <c r="M18" s="17" t="s">
+      <c r="M18" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N18" s="18"/>
+      <c r="N18" s="17"/>
     </row>
     <row r="19" spans="2:14" s="3" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B19" s="25">
+      <c r="B19" s="24">
         <v>1</v>
       </c>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="86" t="s">
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="I19" s="87" t="s">
+      <c r="I19" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="33"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="78"/>
+      <c r="M19" s="32"/>
     </row>
     <row r="20" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="25">
+      <c r="B20" s="24">
         <v>2</v>
       </c>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="33"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="32"/>
     </row>
     <row r="21" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="25">
+      <c r="B21" s="24">
         <v>3</v>
       </c>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="33"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="32"/>
     </row>
     <row r="22" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="25">
+      <c r="B22" s="24">
         <v>4</v>
       </c>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="33"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="32"/>
     </row>
     <row r="23" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="25">
+      <c r="B23" s="24">
         <v>5</v>
       </c>
-      <c r="C23" s="90"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="88"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="33"/>
+      <c r="C23" s="82"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="82"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="32"/>
     </row>
     <row r="24" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="25">
+      <c r="B24" s="24">
         <v>6</v>
       </c>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="90"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="33"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="82"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="32"/>
     </row>
     <row r="25" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="25">
+      <c r="B25" s="24">
         <v>7</v>
       </c>
-      <c r="C25" s="90"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="90"/>
-      <c r="F25" s="90"/>
-      <c r="G25" s="90"/>
-      <c r="H25" s="88"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="33"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="82"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="82"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="32"/>
     </row>
     <row r="26" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="25">
+      <c r="B26" s="24">
         <v>8</v>
       </c>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="88"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="33"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="32"/>
     </row>
     <row r="27" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="25">
+      <c r="B27" s="24">
         <v>9</v>
       </c>
-      <c r="C27" s="90"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="90"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="33"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="32"/>
     </row>
     <row r="28" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="25">
+      <c r="B28" s="24">
         <v>10</v>
       </c>
-      <c r="C28" s="90"/>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="88"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="33"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="32"/>
     </row>
     <row r="29" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="25">
+      <c r="B29" s="24">
         <v>11</v>
       </c>
-      <c r="C29" s="90"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="90"/>
-      <c r="F29" s="90"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="33"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="82"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="32"/>
     </row>
     <row r="30" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="25">
+      <c r="B30" s="24">
         <v>12</v>
       </c>
-      <c r="C30" s="90"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="90"/>
-      <c r="F30" s="90"/>
-      <c r="G30" s="90"/>
-      <c r="H30" s="88"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="33"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="32"/>
     </row>
     <row r="31" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="25">
+      <c r="B31" s="24">
         <v>13</v>
       </c>
-      <c r="C31" s="90"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="90"/>
-      <c r="F31" s="90"/>
-      <c r="G31" s="90"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="33"/>
+      <c r="C31" s="82"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="32"/>
     </row>
     <row r="32" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="25">
+      <c r="B32" s="24">
         <v>14</v>
       </c>
-      <c r="C32" s="90"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="90"/>
-      <c r="F32" s="90"/>
-      <c r="G32" s="90"/>
-      <c r="H32" s="88"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="33"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="32"/>
     </row>
     <row r="33" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="25">
+      <c r="B33" s="24">
         <v>15</v>
       </c>
-      <c r="C33" s="90"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="90"/>
-      <c r="F33" s="90"/>
-      <c r="G33" s="90"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="33"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="32"/>
     </row>
     <row r="34" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="25">
+      <c r="B34" s="24">
         <v>16</v>
       </c>
-      <c r="C34" s="90"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="90"/>
-      <c r="G34" s="90"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="33"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="32"/>
     </row>
     <row r="35" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="25">
+      <c r="B35" s="24">
         <v>17</v>
       </c>
-      <c r="C35" s="90"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="90"/>
-      <c r="F35" s="90"/>
-      <c r="G35" s="90"/>
-      <c r="H35" s="88"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="33"/>
+      <c r="C35" s="82"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="82"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="80"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="32"/>
     </row>
     <row r="36" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="25">
+      <c r="B36" s="24">
         <v>18</v>
       </c>
-      <c r="C36" s="90"/>
-      <c r="D36" s="90"/>
-      <c r="E36" s="90"/>
-      <c r="F36" s="90"/>
-      <c r="G36" s="90"/>
-      <c r="H36" s="88"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="33"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="32"/>
     </row>
     <row r="37" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="25">
+      <c r="B37" s="24">
         <v>19</v>
       </c>
-      <c r="C37" s="90"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="90"/>
-      <c r="F37" s="90"/>
-      <c r="G37" s="90"/>
-      <c r="H37" s="88"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23"/>
-      <c r="M37" s="33"/>
+      <c r="C37" s="82"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="32"/>
     </row>
     <row r="38" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="25">
+      <c r="B38" s="24">
         <v>20</v>
       </c>
-      <c r="C38" s="90"/>
-      <c r="D38" s="90"/>
-      <c r="E38" s="90"/>
-      <c r="F38" s="90"/>
-      <c r="G38" s="90"/>
-      <c r="H38" s="88"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="33"/>
+      <c r="C38" s="82"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="32"/>
     </row>
     <row r="39" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="25">
+      <c r="B39" s="24">
         <v>21</v>
       </c>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90"/>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="90"/>
-      <c r="H39" s="88"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="33"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="32"/>
     </row>
     <row r="40" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="25">
+      <c r="B40" s="24">
         <v>22</v>
       </c>
-      <c r="C40" s="90"/>
-      <c r="D40" s="90"/>
-      <c r="E40" s="90"/>
-      <c r="F40" s="90"/>
-      <c r="G40" s="90"/>
-      <c r="H40" s="88"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="22"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="33"/>
+      <c r="C40" s="82"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="32"/>
     </row>
     <row r="41" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="25">
+      <c r="B41" s="24">
         <v>23</v>
       </c>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="88"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="33"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="80"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="32"/>
     </row>
     <row r="42" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="25">
+      <c r="B42" s="24">
         <v>24</v>
       </c>
-      <c r="C42" s="90"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="90"/>
-      <c r="F42" s="90"/>
-      <c r="G42" s="90"/>
-      <c r="H42" s="88"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="33"/>
+      <c r="C42" s="82"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="82"/>
+      <c r="F42" s="82"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="80"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="32"/>
     </row>
     <row r="43" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="25">
+      <c r="B43" s="24">
         <v>25</v>
       </c>
-      <c r="C43" s="90"/>
-      <c r="D43" s="90"/>
-      <c r="E43" s="90"/>
-      <c r="F43" s="90"/>
-      <c r="G43" s="90"/>
-      <c r="H43" s="88"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="22"/>
-      <c r="K43" s="23"/>
-      <c r="L43" s="23"/>
-      <c r="M43" s="33"/>
+      <c r="C43" s="82"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="82"/>
+      <c r="F43" s="82"/>
+      <c r="G43" s="82"/>
+      <c r="H43" s="80"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="32"/>
     </row>
     <row r="44" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="25"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="30"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="32"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="29"/>
+      <c r="L44" s="29"/>
+      <c r="M44" s="31"/>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B45" s="4"/>
@@ -3136,45 +3144,45 @@
       <c r="L45" s="6"/>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C47" s="55"/>
+      <c r="C47" s="51"/>
     </row>
     <row r="48" spans="2:13" ht="21" x14ac:dyDescent="0.4">
-      <c r="B48" s="126" t="s">
+      <c r="B48" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="G48" s="65"/>
-      <c r="H48" s="128" t="s">
+      <c r="G48" s="57"/>
+      <c r="H48" s="86" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="49" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B49" s="127" t="s">
+      <c r="B49" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="50" t="s">
+      <c r="C49" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="G49" s="75" t="s">
+      <c r="G49" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="H49" s="84">
+      <c r="H49" s="76">
         <v>1</v>
       </c>
-      <c r="I49" s="84">
+      <c r="I49" s="76">
         <v>2</v>
       </c>
-      <c r="J49" s="84">
+      <c r="J49" s="76">
         <v>3</v>
       </c>
-      <c r="K49" s="84">
+      <c r="K49" s="76">
         <v>4</v>
       </c>
-      <c r="L49" s="84">
+      <c r="L49" s="76">
         <v>5</v>
       </c>
     </row>
     <row r="50" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B50" s="91" t="s">
+      <c r="B50" s="83" t="s">
         <v>49</v>
       </c>
       <c r="C50" s="92" t="s">
@@ -3182,32 +3190,32 @@
       </c>
       <c r="D50" s="93"/>
       <c r="E50" s="94"/>
-      <c r="G50" s="76" t="s">
+      <c r="G50" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="H50" s="79">
+      <c r="H50" s="71">
         <f>_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G50), IF(_xlpm.x=0, "", _xlpm.x))</f>
         <v>1</v>
       </c>
-      <c r="I50" s="79" t="str">
+      <c r="I50" s="71" t="str">
         <f t="shared" ref="I50:L51" si="0">_xlfn.LET(_xlpm.x, COUNTIF(I$19:I$43, $G50), IF(_xlpm.x=0, "", _xlpm.x))</f>
         <v/>
       </c>
-      <c r="J50" s="79" t="str">
+      <c r="J50" s="71" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K50" s="79" t="str">
+      <c r="K50" s="71" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L50" s="79" t="str">
+      <c r="L50" s="71" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B51" s="64" t="s">
+      <c r="B51" s="56" t="s">
         <v>68</v>
       </c>
       <c r="C51" s="92" t="s">
@@ -3215,134 +3223,139 @@
       </c>
       <c r="D51" s="93"/>
       <c r="E51" s="94"/>
-      <c r="G51" s="77" t="s">
+      <c r="G51" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="H51" s="79" t="str">
+      <c r="H51" s="71" t="str">
         <f>_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G51), IF(_xlpm.x=0, "", _xlpm.x))</f>
         <v/>
       </c>
-      <c r="I51" s="79">
+      <c r="I51" s="71">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J51" s="79" t="str">
+      <c r="J51" s="71" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K51" s="79" t="str">
+      <c r="K51" s="71" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L51" s="79" t="str">
+      <c r="L51" s="71" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="52" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B52" s="58"/>
+      <c r="B52" s="54"/>
       <c r="C52" s="92"/>
       <c r="D52" s="93"/>
       <c r="E52" s="94"/>
-      <c r="G52" s="78"/>
-      <c r="H52" s="79" t="str">
+      <c r="G52" s="70"/>
+      <c r="H52" s="71" t="str">
         <f t="shared" ref="H52:L55" si="1">_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G52), IF(_xlpm.x=0, "", _xlpm.x))</f>
         <v/>
       </c>
-      <c r="I52" s="79" t="str">
+      <c r="I52" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J52" s="79" t="str">
+      <c r="J52" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K52" s="79" t="str">
+      <c r="K52" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L52" s="79" t="str">
+      <c r="L52" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="2:12" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="G53" s="65"/>
-      <c r="H53" s="79" t="str">
+      <c r="G53" s="57"/>
+      <c r="H53" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I53" s="79" t="str">
+      <c r="I53" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J53" s="79" t="str">
+      <c r="J53" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K53" s="79" t="str">
+      <c r="K53" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L53" s="79" t="str">
+      <c r="L53" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="2:12" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="G54" s="65"/>
-      <c r="H54" s="79" t="str">
+      <c r="G54" s="57"/>
+      <c r="H54" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I54" s="79" t="str">
+      <c r="I54" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J54" s="79" t="str">
+      <c r="J54" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K54" s="79" t="str">
+      <c r="K54" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L54" s="79" t="str">
+      <c r="L54" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="55" spans="2:12" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="G55" s="65"/>
-      <c r="H55" s="79" t="str">
+      <c r="G55" s="57"/>
+      <c r="H55" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I55" s="79" t="str">
+      <c r="I55" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J55" s="79" t="str">
+      <c r="J55" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K55" s="79" t="str">
+      <c r="K55" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L55" s="79" t="str">
+      <c r="L55" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="H56" s="65"/>
+      <c r="H56" s="57"/>
     </row>
     <row r="59" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="60" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="61" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="H17:L17"/>
@@ -3354,11 +3367,6 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3390,14 +3398,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3417,15 +3425,15 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="101" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="97"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
       <c r="N4" s="14"/>
@@ -3434,15 +3442,15 @@
       <c r="U4" s="2"/>
     </row>
     <row r="5" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="97"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
       <c r="N5" s="14"/>
@@ -3456,164 +3464,164 @@
     </row>
     <row r="7" spans="2:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
       <c r="N7" s="14"/>
     </row>
     <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
       <c r="N8" s="14"/>
     </row>
     <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
       <c r="N9" s="14"/>
     </row>
     <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="56"/>
-      <c r="C10" s="57"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="53"/>
       <c r="D10" s="92"/>
       <c r="E10" s="93"/>
       <c r="F10" s="94"/>
-      <c r="H10" s="24"/>
+      <c r="H10" s="23"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="56"/>
-      <c r="C11" s="57"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="92"/>
       <c r="E11" s="93"/>
       <c r="F11" s="94"/>
-      <c r="H11" s="24"/>
+      <c r="H11" s="23"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="56"/>
-      <c r="C12" s="57"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="92"/>
       <c r="E12" s="93"/>
       <c r="F12" s="94"/>
-      <c r="H12" s="24"/>
+      <c r="H12" s="23"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="56"/>
-      <c r="C13" s="57"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="53"/>
       <c r="D13" s="92"/>
       <c r="E13" s="93"/>
       <c r="F13" s="94"/>
-      <c r="H13" s="24"/>
+      <c r="H13" s="23"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="56"/>
-      <c r="C14" s="57"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="53"/>
       <c r="D14" s="92"/>
       <c r="E14" s="93"/>
       <c r="F14" s="94"/>
-      <c r="H14" s="24"/>
+      <c r="H14" s="23"/>
       <c r="N14" s="14"/>
     </row>
     <row r="15" spans="2:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="48"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
       <c r="N15" s="14"/>
     </row>
     <row r="16" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="53"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="2:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="124" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="53"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="58"/>
+      <c r="B18" s="54"/>
       <c r="C18" s="92"/>
       <c r="D18" s="93"/>
       <c r="E18" s="94"/>
-      <c r="H18" s="24"/>
+      <c r="H18" s="23"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="58"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="92"/>
       <c r="D19" s="93"/>
       <c r="E19" s="94"/>
-      <c r="H19" s="24"/>
+      <c r="H19" s="23"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="58"/>
+      <c r="B20" s="54"/>
       <c r="C20" s="92"/>
       <c r="D20" s="93"/>
       <c r="E20" s="94"/>
-      <c r="H20" s="24"/>
+      <c r="H20" s="23"/>
       <c r="N20" s="14"/>
     </row>
     <row r="21" spans="2:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="48"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
       <c r="N21" s="14"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B22" s="19"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
       <c r="N22" s="14"/>
     </row>
     <row r="23" spans="2:14" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="123" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="10"/>
-      <c r="D23" s="20"/>
+      <c r="D23" s="19"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="34"/>
+      <c r="G23" s="33"/>
       <c r="H23" s="1"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
@@ -3622,10 +3630,15 @@
       <c r="N23" s="14"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C26" s="51"/>
+      <c r="C26" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D12:F12"/>
@@ -3634,11 +3647,6 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3670,14 +3678,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3697,22 +3705,22 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="101" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="97"/>
     </row>
     <row r="5" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="97"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
@@ -3722,139 +3730,139 @@
       <c r="N7" s="14"/>
     </row>
     <row r="8" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
       <c r="N8" s="14"/>
     </row>
     <row r="9" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
       <c r="N9" s="14"/>
     </row>
     <row r="10" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="56"/>
-      <c r="C10" s="57"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="53"/>
       <c r="D10" s="92"/>
       <c r="E10" s="93"/>
       <c r="F10" s="94"/>
-      <c r="H10" s="24"/>
+      <c r="H10" s="23"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="56"/>
-      <c r="C11" s="57"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="92"/>
       <c r="E11" s="93"/>
       <c r="F11" s="94"/>
-      <c r="H11" s="24"/>
+      <c r="H11" s="23"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="56"/>
-      <c r="C12" s="57"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="92"/>
       <c r="E12" s="93"/>
       <c r="F12" s="94"/>
-      <c r="H12" s="24"/>
+      <c r="H12" s="23"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="B13" s="56"/>
-      <c r="C13" s="57"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="53"/>
       <c r="D13" s="92"/>
       <c r="E13" s="93"/>
       <c r="F13" s="94"/>
-      <c r="H13" s="24"/>
+      <c r="H13" s="23"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="B14" s="56"/>
-      <c r="C14" s="57"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="53"/>
       <c r="D14" s="92"/>
       <c r="E14" s="93"/>
       <c r="F14" s="94"/>
-      <c r="H14" s="24"/>
+      <c r="H14" s="23"/>
       <c r="N14" s="14"/>
     </row>
     <row r="15" spans="2:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="B15" s="48"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
       <c r="N15" s="14"/>
     </row>
     <row r="16" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="53"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="124" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="53"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="58"/>
+      <c r="B18" s="54"/>
       <c r="C18" s="92"/>
       <c r="D18" s="93"/>
       <c r="E18" s="94"/>
-      <c r="H18" s="24"/>
+      <c r="H18" s="23"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="B19" s="58"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="92"/>
       <c r="D19" s="93"/>
       <c r="E19" s="94"/>
-      <c r="H19" s="24"/>
+      <c r="H19" s="23"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="B20" s="58"/>
+      <c r="B20" s="54"/>
       <c r="C20" s="92"/>
       <c r="D20" s="93"/>
       <c r="E20" s="94"/>
-      <c r="H20" s="24"/>
+      <c r="H20" s="23"/>
       <c r="N20" s="14"/>
     </row>
     <row r="21" spans="2:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="B21" s="48"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
       <c r="N21" s="14"/>
     </row>
     <row r="22" spans="2:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="123" t="s">
         <v>44</v>
       </c>
       <c r="N22" s="14"/>
@@ -3873,11 +3881,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D12:F12"/>
@@ -3886,6 +3889,11 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3906,64 +3914,64 @@
     <row r="3" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="109"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="111"/>
     </row>
     <row r="6" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="110" t="s">
+      <c r="B6" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="110"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="109"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="111"/>
     </row>
     <row r="7" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="104"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
     </row>
     <row r="9" spans="2:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="125" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="126" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="114"/>
-      <c r="C11" s="115"/>
-      <c r="D11" s="115"/>
-      <c r="E11" s="115"/>
-      <c r="F11" s="115"/>
-      <c r="G11" s="115"/>
-      <c r="H11" s="115"/>
-      <c r="I11" s="115"/>
-      <c r="J11" s="116"/>
+      <c r="B11" s="106"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="107"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107"/>
+      <c r="J11" s="108"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="14"/>
@@ -3972,61 +3980,61 @@
       <c r="E12" s="14"/>
     </row>
     <row r="13" spans="2:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="126" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="114"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="116"/>
+      <c r="B14" s="106"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+      <c r="F14" s="107"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="107"/>
+      <c r="J14" s="108"/>
     </row>
     <row r="16" spans="2:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="126" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="116"/>
+      <c r="B17" s="106"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="107"/>
+      <c r="F17" s="107"/>
+      <c r="G17" s="107"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="108"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
     </row>
     <row r="19" spans="2:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="114"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="115"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="116"/>
+      <c r="B20" s="106"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="108"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="14"/>
@@ -4035,7 +4043,7 @@
       <c r="E21" s="14"/>
     </row>
     <row r="22" spans="2:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="128" t="s">
         <v>66</v>
       </c>
       <c r="C22" s="14"/>
@@ -4043,49 +4051,49 @@
       <c r="E22" s="14"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="114"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="116"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="107"/>
+      <c r="E23" s="107"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="107"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="107"/>
+      <c r="J23" s="108"/>
     </row>
     <row r="25" spans="2:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="B25" s="45" t="s">
+      <c r="B25" s="122" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="46" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B27" s="64"/>
-      <c r="C27" s="111"/>
-      <c r="D27" s="112"/>
-      <c r="E27" s="112"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="113"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="105"/>
     </row>
     <row r="28" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B28" s="64"/>
-      <c r="C28" s="111"/>
-      <c r="D28" s="112"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="112"/>
-      <c r="G28" s="112"/>
-      <c r="H28" s="113"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="105"/>
     </row>
     <row r="29" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B29" s="64"/>
+      <c r="B29" s="56"/>
       <c r="C29" s="92"/>
       <c r="D29" s="93"/>
       <c r="E29" s="93"/>
@@ -4097,12 +4105,18 @@
       <c r="B30" s="8"/>
     </row>
     <row r="31" spans="2:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="123" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:J7"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="B11:J11"/>
@@ -4111,12 +4125,6 @@
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="C27:H27"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4149,14 +4157,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -4176,15 +4184,15 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="120" t="s">
+      <c r="B4" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="121"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="123"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="119"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
       <c r="N4" s="14"/>
@@ -4201,7 +4209,7 @@
       <c r="N5" s="14"/>
     </row>
     <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="122" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="7"/>
@@ -4211,111 +4219,126 @@
       <c r="N6" s="14"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B7" s="54"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="119"/>
-      <c r="G7" s="65"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="115"/>
+      <c r="G7" s="57"/>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B8" s="130"/>
     </row>
     <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="51"/>
+      <c r="C9" s="47"/>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C10" s="117"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="119"/>
-      <c r="G10" s="65"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="115"/>
+      <c r="G10" s="57"/>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B11" s="130"/>
     </row>
     <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="122" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="119"/>
-      <c r="G13" s="65"/>
+      <c r="B13" s="130"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="G13" s="57"/>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B14" s="130"/>
     </row>
     <row r="15" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="122" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="119"/>
-      <c r="G16" s="65"/>
+      <c r="B16" s="130"/>
+      <c r="C16" s="113"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="115"/>
+      <c r="G16" s="57"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="130"/>
     </row>
     <row r="18" spans="2:5" ht="21" x14ac:dyDescent="0.3">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="122" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C19" s="66" t="s">
+      <c r="C19" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="67" t="s">
+      <c r="D19" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="68" t="s">
+      <c r="E19" s="60" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="69"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="80"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="72"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C21" s="71"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="81"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="73"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C22" s="71"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="81"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="73"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C23" s="71"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="81"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="73"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C24" s="71"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="81"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="73"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C25" s="71"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="81"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="73"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C26" s="71"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="81"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="73"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C27" s="71"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="81"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="73"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C28" s="71"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="81"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="73"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C29" s="73"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="82"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4345,10 +4368,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="38" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -4357,150 +4380,145 @@
       <c r="H2" s="14"/>
     </row>
     <row r="3" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="124" t="s">
+      <c r="C3" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="124"/>
-      <c r="F3" s="125" t="s">
+      <c r="D3" s="121"/>
+      <c r="F3" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="124" t="s">
+      <c r="C4" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="124"/>
-      <c r="F4" s="36" t="s">
+      <c r="D4" s="121"/>
+      <c r="F4" s="35" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="124" t="s">
+      <c r="C5" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="124"/>
-      <c r="F5" s="36" t="s">
+      <c r="D5" s="121"/>
+      <c r="F5" s="35" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="14"/>
     </row>
     <row r="6" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="124" t="s">
+      <c r="C6" s="121" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="124"/>
-      <c r="F6" s="37" t="s">
+      <c r="D6" s="121"/>
+      <c r="F6" s="36" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="14"/>
     </row>
     <row r="7" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="124" t="s">
+      <c r="C7" s="121" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="124"/>
-      <c r="F7" s="35" t="s">
+      <c r="D7" s="121"/>
+      <c r="F7" s="34" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="14"/>
     </row>
     <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="124" t="s">
+      <c r="C8" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="124"/>
+      <c r="D8" s="121"/>
     </row>
     <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="124" t="s">
+      <c r="C9" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="124"/>
+      <c r="D9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="124" t="s">
+      <c r="C10" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="124"/>
+      <c r="D10" s="121"/>
     </row>
     <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="124" t="s">
+      <c r="C11" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="124"/>
+      <c r="D11" s="121"/>
     </row>
     <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="124" t="s">
+      <c r="C12" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="124"/>
+      <c r="D12" s="121"/>
     </row>
     <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="42"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="39"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="124" t="s">
+      <c r="C14" s="121" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="124"/>
+      <c r="D14" s="121"/>
     </row>
     <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="41"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="124"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="121"/>
     </row>
     <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="124" t="s">
+      <c r="C16" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="124"/>
+      <c r="D16" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
@@ -4510,18 +4528,42 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
+    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4797,37 +4839,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
-    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4853,19 +4886,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/assets/files/Audit_Workpaper_Template.xlsx
+++ b/assets/files/Audit_Workpaper_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fjmgt-my.sharepoint.com/personal/colby_kellersberger_fjmgt_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2246" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D0302E5-3476-4AEB-B65B-57DC46F5EE9F}"/>
+  <xr:revisionPtr revIDLastSave="2254" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD33A260-FEE7-410B-8252-231157B86D56}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="1116" windowWidth="29772" windowHeight="22392" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="72">
   <si>
     <t>Tickmark</t>
   </si>
@@ -181,9 +181,6 @@
     <t>Explanation</t>
   </si>
   <si>
-    <t>Documentation Testing</t>
-  </si>
-  <si>
     <t>Schedule Testing</t>
   </si>
   <si>
@@ -263,6 +260,12 @@
   </si>
   <si>
     <t xml:space="preserve">Exception noted. </t>
+  </si>
+  <si>
+    <t>Screenshot Placeholder</t>
+  </si>
+  <si>
+    <t>Figure 1 – [Placeholder]</t>
   </si>
 </sst>
 </file>
@@ -714,7 +717,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -921,6 +924,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF404040"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1506,7 +1515,7 @@
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1786,6 +1795,48 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -1800,15 +1851,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1818,21 +1860,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1851,18 +1896,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1882,39 +1915,20 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="44" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
@@ -2512,14 +2526,14 @@
   <sheetData>
     <row r="1" spans="2:20" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:20" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -2537,13 +2551,13 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="89" t="s">
+      <c r="B4" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="90"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="97"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="109"/>
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
       <c r="J4" s="13"/>
@@ -2553,13 +2567,13 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="100" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="98"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="97"/>
+      <c r="B5" s="102" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="100"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="109"/>
       <c r="H5" s="55"/>
       <c r="I5" s="55"/>
       <c r="J5" s="12"/>
@@ -2569,13 +2583,13 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="98" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="99"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="96"/>
-      <c r="F6" s="97"/>
+      <c r="B6" s="100" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="101"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="109"/>
       <c r="H6" s="55"/>
       <c r="I6" s="55"/>
       <c r="J6" s="12"/>
@@ -2609,9 +2623,9 @@
         <v>1</v>
       </c>
       <c r="C10" s="77"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="94"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="99"/>
       <c r="H10" s="23"/>
     </row>
     <row r="11" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2619,9 +2633,9 @@
         <v>2</v>
       </c>
       <c r="C11" s="77"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="94"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="99"/>
       <c r="H11" s="23"/>
     </row>
     <row r="12" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2629,9 +2643,9 @@
         <v>3</v>
       </c>
       <c r="C12" s="77"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="94"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
       <c r="H12" s="23"/>
     </row>
     <row r="13" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2639,9 +2653,9 @@
         <v>4</v>
       </c>
       <c r="C13" s="77"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="94"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="99"/>
       <c r="H13" s="23"/>
     </row>
     <row r="14" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2649,9 +2663,9 @@
         <v>5</v>
       </c>
       <c r="C14" s="77"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="94"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="99"/>
       <c r="H14" s="23"/>
     </row>
     <row r="15" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2675,13 +2689,13 @@
       <c r="B17" s="1"/>
       <c r="F17" s="57"/>
       <c r="G17" s="57"/>
-      <c r="H17" s="91" t="s">
-        <v>57</v>
-      </c>
-      <c r="I17" s="91"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="91"/>
+      <c r="H17" s="106" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="106"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
+      <c r="L17" s="106"/>
     </row>
     <row r="18" spans="2:14" s="30" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="15" t="s">
@@ -2708,7 +2722,7 @@
         <v>5</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N18" s="17"/>
     </row>
@@ -2722,10 +2736,10 @@
       <c r="F19" s="81"/>
       <c r="G19" s="81"/>
       <c r="H19" s="78" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I19" s="79" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J19" s="78"/>
       <c r="K19" s="78"/>
@@ -3148,11 +3162,11 @@
     </row>
     <row r="48" spans="2:13" ht="21" x14ac:dyDescent="0.4">
       <c r="B48" s="84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G48" s="57"/>
       <c r="H48" s="86" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -3163,7 +3177,7 @@
         <v>42</v>
       </c>
       <c r="G49" s="67" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H49" s="76">
         <v>1</v>
@@ -3183,15 +3197,15 @@
     </row>
     <row r="50" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B50" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="C50" s="92" t="s">
-        <v>69</v>
-      </c>
-      <c r="D50" s="93"/>
-      <c r="E50" s="94"/>
+        <v>48</v>
+      </c>
+      <c r="C50" s="97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" s="98"/>
+      <c r="E50" s="99"/>
       <c r="G50" s="68" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H50" s="71">
         <f>_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G50), IF(_xlpm.x=0, "", _xlpm.x))</f>
@@ -3216,15 +3230,15 @@
     </row>
     <row r="51" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B51" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C51" s="92" t="s">
-        <v>70</v>
-      </c>
-      <c r="D51" s="93"/>
-      <c r="E51" s="94"/>
+        <v>67</v>
+      </c>
+      <c r="C51" s="97" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" s="98"/>
+      <c r="E51" s="99"/>
       <c r="G51" s="69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H51" s="71" t="str">
         <f>_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G51), IF(_xlpm.x=0, "", _xlpm.x))</f>
@@ -3249,9 +3263,9 @@
     </row>
     <row r="52" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B52" s="54"/>
-      <c r="C52" s="92"/>
-      <c r="D52" s="93"/>
-      <c r="E52" s="94"/>
+      <c r="C52" s="97"/>
+      <c r="D52" s="98"/>
+      <c r="E52" s="99"/>
       <c r="G52" s="70"/>
       <c r="H52" s="71" t="str">
         <f t="shared" ref="H52:L55" si="1">_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G52), IF(_xlpm.x=0, "", _xlpm.x))</f>
@@ -3351,11 +3365,6 @@
     <row r="61" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="H17:L17"/>
@@ -3367,6 +3376,11 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3376,7 +3390,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C2776A-E04F-41FD-B3D7-35684437E078}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="B1:U26"/>
+  <dimension ref="B1:U51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.5546875" customWidth="1"/>
@@ -3398,14 +3412,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3425,13 +3439,13 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="101" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="97"/>
+      <c r="B4" s="110" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="111"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="109"/>
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
       <c r="J4" s="13"/>
@@ -3442,13 +3456,13 @@
       <c r="U4" s="2"/>
     </row>
     <row r="5" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="101" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="97"/>
+      <c r="B5" s="110" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="111"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="109"/>
       <c r="H5" s="55"/>
       <c r="I5" s="55"/>
       <c r="J5" s="13"/>
@@ -3473,8 +3487,8 @@
       <c r="N7" s="14"/>
     </row>
     <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B8" s="122" t="s">
-        <v>55</v>
+      <c r="B8" s="88" t="s">
+        <v>54</v>
       </c>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
@@ -3497,45 +3511,45 @@
     <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="52"/>
       <c r="C10" s="53"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="94"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="99"/>
       <c r="H10" s="23"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="52"/>
       <c r="C11" s="53"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="94"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="99"/>
       <c r="H11" s="23"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="52"/>
       <c r="C12" s="53"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="94"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
       <c r="H12" s="23"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="52"/>
       <c r="C13" s="53"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="94"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="99"/>
       <c r="H13" s="23"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="52"/>
       <c r="C14" s="53"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="94"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="99"/>
       <c r="H14" s="23"/>
       <c r="N14" s="14"/>
     </row>
@@ -3550,8 +3564,8 @@
       <c r="N15" s="14"/>
     </row>
     <row r="16" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B16" s="122" t="s">
-        <v>56</v>
+      <c r="B16" s="88" t="s">
+        <v>55</v>
       </c>
       <c r="F16" s="49"/>
       <c r="G16" s="23"/>
@@ -3562,7 +3576,7 @@
       <c r="B17" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="124" t="s">
+      <c r="C17" s="90" t="s">
         <v>42</v>
       </c>
       <c r="F17" s="49"/>
@@ -3572,25 +3586,25 @@
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="54"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="94"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="99"/>
       <c r="H18" s="23"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="54"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="94"/>
+      <c r="C19" s="97"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="99"/>
       <c r="H19" s="23"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="54"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="99"/>
       <c r="H20" s="23"/>
       <c r="N20" s="14"/>
     </row>
@@ -3614,8 +3628,8 @@
       <c r="N22" s="14"/>
     </row>
     <row r="23" spans="2:14" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="B23" s="123" t="s">
-        <v>43</v>
+      <c r="B23" s="89" t="s">
+        <v>71</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="19"/>
@@ -3629,16 +3643,254 @@
       <c r="L23" s="9"/>
       <c r="N23" s="14"/>
     </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C25" s="131"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="131"/>
+      <c r="I25" s="131"/>
+    </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C26" s="47"/>
+      <c r="C26" s="132"/>
+      <c r="D26" s="131"/>
+      <c r="E26" s="131"/>
+      <c r="F26" s="131"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="131"/>
+      <c r="I26" s="131"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C27" s="131"/>
+      <c r="D27" s="131"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="131"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C28" s="131"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="131"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="131"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="131"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C30" s="131"/>
+      <c r="D30" s="131"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="131"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="131"/>
+      <c r="I30" s="131"/>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C31" s="131"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="131"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C32" s="131"/>
+      <c r="D32" s="131"/>
+      <c r="E32" s="131"/>
+      <c r="F32" s="131"/>
+      <c r="G32" s="131"/>
+      <c r="H32" s="131"/>
+      <c r="I32" s="131"/>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="131"/>
+      <c r="D33" s="131"/>
+      <c r="E33" s="131"/>
+      <c r="F33" s="131"/>
+      <c r="G33" s="131"/>
+      <c r="H33" s="131"/>
+      <c r="I33" s="131"/>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="131"/>
+      <c r="D34" s="131"/>
+      <c r="E34" s="131"/>
+      <c r="F34" s="131"/>
+      <c r="G34" s="131"/>
+      <c r="H34" s="131"/>
+      <c r="I34" s="131"/>
+    </row>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C35" s="131"/>
+      <c r="D35" s="131"/>
+      <c r="E35" s="131"/>
+      <c r="F35" s="131"/>
+      <c r="G35" s="131"/>
+      <c r="H35" s="131"/>
+      <c r="I35" s="131"/>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C36" s="131"/>
+      <c r="D36" s="133" t="s">
+        <v>70</v>
+      </c>
+      <c r="E36" s="133"/>
+      <c r="F36" s="133"/>
+      <c r="G36" s="133"/>
+      <c r="H36" s="131"/>
+      <c r="I36" s="131"/>
+    </row>
+    <row r="37" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C37" s="131"/>
+      <c r="D37" s="131"/>
+      <c r="E37" s="131"/>
+      <c r="F37" s="131"/>
+      <c r="G37" s="131"/>
+      <c r="H37" s="131"/>
+      <c r="I37" s="131"/>
+    </row>
+    <row r="38" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C38" s="131"/>
+      <c r="D38" s="131"/>
+      <c r="E38" s="131"/>
+      <c r="F38" s="131"/>
+      <c r="G38" s="131"/>
+      <c r="H38" s="131"/>
+      <c r="I38" s="131"/>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C39" s="131"/>
+      <c r="D39" s="131"/>
+      <c r="E39" s="131"/>
+      <c r="F39" s="131"/>
+      <c r="G39" s="131"/>
+      <c r="H39" s="131"/>
+      <c r="I39" s="131"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C40" s="131"/>
+      <c r="D40" s="131"/>
+      <c r="E40" s="131"/>
+      <c r="F40" s="131"/>
+      <c r="G40" s="131"/>
+      <c r="H40" s="131"/>
+      <c r="I40" s="131"/>
+    </row>
+    <row r="41" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C41" s="131"/>
+      <c r="D41" s="131"/>
+      <c r="E41" s="131"/>
+      <c r="F41" s="131"/>
+      <c r="G41" s="131"/>
+      <c r="H41" s="131"/>
+      <c r="I41" s="131"/>
+    </row>
+    <row r="42" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C42" s="131"/>
+      <c r="D42" s="131"/>
+      <c r="E42" s="131"/>
+      <c r="F42" s="131"/>
+      <c r="G42" s="131"/>
+      <c r="H42" s="131"/>
+      <c r="I42" s="131"/>
+    </row>
+    <row r="43" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C43" s="131"/>
+      <c r="D43" s="131"/>
+      <c r="E43" s="131"/>
+      <c r="F43" s="131"/>
+      <c r="G43" s="131"/>
+      <c r="H43" s="131"/>
+      <c r="I43" s="131"/>
+    </row>
+    <row r="44" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C44" s="131"/>
+      <c r="D44" s="131"/>
+      <c r="E44" s="131"/>
+      <c r="F44" s="131"/>
+      <c r="G44" s="131"/>
+      <c r="H44" s="131"/>
+      <c r="I44" s="131"/>
+    </row>
+    <row r="45" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C45" s="131"/>
+      <c r="D45" s="131"/>
+      <c r="E45" s="131"/>
+      <c r="F45" s="131"/>
+      <c r="G45" s="131"/>
+      <c r="H45" s="131"/>
+      <c r="I45" s="131"/>
+    </row>
+    <row r="46" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C46" s="131"/>
+      <c r="D46" s="131"/>
+      <c r="E46" s="131"/>
+      <c r="F46" s="131"/>
+      <c r="G46" s="131"/>
+      <c r="H46" s="131"/>
+      <c r="I46" s="131"/>
+    </row>
+    <row r="47" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C47" s="131"/>
+      <c r="D47" s="131"/>
+      <c r="E47" s="131"/>
+      <c r="F47" s="131"/>
+      <c r="G47" s="131"/>
+      <c r="H47" s="131"/>
+      <c r="I47" s="131"/>
+    </row>
+    <row r="48" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C48" s="131"/>
+      <c r="D48" s="131"/>
+      <c r="E48" s="131"/>
+      <c r="F48" s="131"/>
+      <c r="G48" s="131"/>
+      <c r="H48" s="131"/>
+      <c r="I48" s="131"/>
+    </row>
+    <row r="49" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C49" s="131"/>
+      <c r="D49" s="131"/>
+      <c r="E49" s="131"/>
+      <c r="F49" s="131"/>
+      <c r="G49" s="131"/>
+      <c r="H49" s="131"/>
+      <c r="I49" s="131"/>
+    </row>
+    <row r="50" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C50" s="131"/>
+      <c r="D50" s="131"/>
+      <c r="E50" s="131"/>
+      <c r="F50" s="131"/>
+      <c r="G50" s="131"/>
+      <c r="H50" s="131"/>
+      <c r="I50" s="131"/>
+    </row>
+    <row r="51" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C51" s="131"/>
+      <c r="D51" s="131"/>
+      <c r="E51" s="131"/>
+      <c r="F51" s="131"/>
+      <c r="G51" s="131"/>
+      <c r="H51" s="131"/>
+      <c r="I51" s="131"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:F5"/>
+  <mergeCells count="14">
+    <mergeCell ref="D36:G36"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D12:F12"/>
@@ -3647,6 +3899,11 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3678,14 +3935,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3705,22 +3962,22 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="101" t="s">
+      <c r="B4" s="110" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="111"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="109"/>
+    </row>
+    <row r="5" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="97"/>
-    </row>
-    <row r="5" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="101" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="97"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="109"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
@@ -3730,8 +3987,8 @@
       <c r="N7" s="14"/>
     </row>
     <row r="8" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="122" t="s">
-        <v>55</v>
+      <c r="B8" s="88" t="s">
+        <v>54</v>
       </c>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
@@ -3754,45 +4011,45 @@
     <row r="10" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="52"/>
       <c r="C10" s="53"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="94"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="99"/>
       <c r="H10" s="23"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="52"/>
       <c r="C11" s="53"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="94"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="99"/>
       <c r="H11" s="23"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="52"/>
       <c r="C12" s="53"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="94"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
       <c r="H12" s="23"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B13" s="52"/>
       <c r="C13" s="53"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="94"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="99"/>
       <c r="H13" s="23"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B14" s="52"/>
       <c r="C14" s="53"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="94"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="99"/>
       <c r="H14" s="23"/>
       <c r="N14" s="14"/>
     </row>
@@ -3807,8 +4064,8 @@
       <c r="N15" s="14"/>
     </row>
     <row r="16" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="122" t="s">
-        <v>56</v>
+      <c r="B16" s="88" t="s">
+        <v>55</v>
       </c>
       <c r="F16" s="49"/>
       <c r="G16" s="23"/>
@@ -3819,7 +4076,7 @@
       <c r="B17" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="124" t="s">
+      <c r="C17" s="90" t="s">
         <v>42</v>
       </c>
       <c r="F17" s="49"/>
@@ -3829,25 +4086,25 @@
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="54"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="94"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="99"/>
       <c r="H18" s="23"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B19" s="54"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="94"/>
+      <c r="C19" s="97"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="99"/>
       <c r="H19" s="23"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B20" s="54"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="99"/>
       <c r="H20" s="23"/>
       <c r="N20" s="14"/>
     </row>
@@ -3862,8 +4119,8 @@
       <c r="N21" s="14"/>
     </row>
     <row r="22" spans="2:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="B22" s="123" t="s">
-        <v>44</v>
+      <c r="B22" s="89" t="s">
+        <v>43</v>
       </c>
       <c r="N22" s="14"/>
     </row>
@@ -3881,6 +4138,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D12:F12"/>
@@ -3889,11 +4151,6 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3914,64 +4171,64 @@
     <row r="3" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="110" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="112" t="s">
+      <c r="B6" s="115" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="115"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="114"/>
+    </row>
+    <row r="7" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="112"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="111"/>
-    </row>
-    <row r="7" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="98" t="s">
+      <c r="C7" s="100"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="109"/>
+    </row>
+    <row r="9" spans="2:10" ht="21" x14ac:dyDescent="0.3">
+      <c r="B9" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="98"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="97"/>
-    </row>
-    <row r="9" spans="2:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="B9" s="125" t="s">
+    </row>
+    <row r="10" spans="2:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="B10" s="92" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="B10" s="126" t="s">
-        <v>62</v>
-      </c>
-    </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="106"/>
-      <c r="C11" s="107"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="107"/>
-      <c r="F11" s="107"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="107"/>
-      <c r="I11" s="107"/>
-      <c r="J11" s="108"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="120"/>
+      <c r="H11" s="120"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="14"/>
@@ -3980,36 +4237,36 @@
       <c r="E12" s="14"/>
     </row>
     <row r="13" spans="2:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="B13" s="126" t="s">
+      <c r="B13" s="92" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="119"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="120"/>
+      <c r="J14" s="121"/>
+    </row>
+    <row r="16" spans="2:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="B16" s="92" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="106"/>
-      <c r="C14" s="107"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="107"/>
-      <c r="G14" s="107"/>
-      <c r="H14" s="107"/>
-      <c r="I14" s="107"/>
-      <c r="J14" s="108"/>
-    </row>
-    <row r="16" spans="2:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="B16" s="126" t="s">
-        <v>64</v>
-      </c>
-    </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="106"/>
-      <c r="C17" s="107"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="107"/>
-      <c r="F17" s="107"/>
-      <c r="G17" s="107"/>
-      <c r="H17" s="107"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="108"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="120"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="121"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="50"/>
@@ -4018,23 +4275,23 @@
       <c r="E18" s="50"/>
     </row>
     <row r="19" spans="2:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="B19" s="127" t="s">
-        <v>65</v>
+      <c r="B19" s="93" t="s">
+        <v>64</v>
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="50"/>
       <c r="E19" s="50"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="106"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="107"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="107"/>
-      <c r="J20" s="108"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="121"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="14"/>
@@ -4043,26 +4300,26 @@
       <c r="E21" s="14"/>
     </row>
     <row r="22" spans="2:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="B22" s="128" t="s">
-        <v>66</v>
+      <c r="B22" s="94" t="s">
+        <v>65</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="107"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="107"/>
-      <c r="J23" s="108"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="120"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="120"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="120"/>
+      <c r="J23" s="121"/>
     </row>
     <row r="25" spans="2:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="B25" s="122" t="s">
+      <c r="B25" s="88" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4076,47 +4333,41 @@
     </row>
     <row r="27" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B27" s="56"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="104"/>
-      <c r="G27" s="104"/>
-      <c r="H27" s="105"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="118"/>
     </row>
     <row r="28" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B28" s="56"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="105"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="118"/>
     </row>
     <row r="29" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B29" s="56"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="94"/>
+      <c r="C29" s="97"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="99"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="8"/>
     </row>
     <row r="31" spans="2:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="B31" s="123" t="s">
-        <v>67</v>
+      <c r="B31" s="89" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:J7"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="B11:J11"/>
@@ -4125,6 +4376,12 @@
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="C27:H27"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4157,14 +4414,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -4184,12 +4441,12 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="116" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="117"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="119"/>
+      <c r="B4" s="125" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="126"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="128"/>
       <c r="G4" s="57"/>
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
@@ -4209,7 +4466,7 @@
       <c r="N5" s="14"/>
     </row>
     <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B6" s="122" t="s">
+      <c r="B6" s="88" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="7"/>
@@ -4219,75 +4476,75 @@
       <c r="N6" s="14"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B7" s="129"/>
-      <c r="C7" s="113"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="115"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="124"/>
       <c r="G7" s="57"/>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B8" s="130"/>
+      <c r="B8" s="96"/>
     </row>
     <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B9" s="122" t="s">
+      <c r="B9" s="88" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="47"/>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B10" s="96"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="124"/>
+      <c r="G10" s="57"/>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B11" s="96"/>
+    </row>
+    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.3">
+      <c r="B12" s="88" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B13" s="96"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="124"/>
+      <c r="G13" s="57"/>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B14" s="96"/>
+    </row>
+    <row r="15" spans="2:21" ht="21" x14ac:dyDescent="0.3">
+      <c r="B15" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="47"/>
-    </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B10" s="130"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="114"/>
-      <c r="E10" s="115"/>
-      <c r="G10" s="57"/>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B11" s="130"/>
-    </row>
-    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B12" s="122" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B13" s="130"/>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="115"/>
-      <c r="G13" s="57"/>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B14" s="130"/>
-    </row>
-    <row r="15" spans="2:21" ht="21" x14ac:dyDescent="0.3">
-      <c r="B15" s="122" t="s">
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B16" s="96"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="124"/>
+      <c r="G16" s="57"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="96"/>
+    </row>
+    <row r="18" spans="2:5" ht="21" x14ac:dyDescent="0.3">
+      <c r="B18" s="88" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B16" s="130"/>
-      <c r="C16" s="113"/>
-      <c r="D16" s="114"/>
-      <c r="E16" s="115"/>
-      <c r="G16" s="57"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="130"/>
-    </row>
-    <row r="18" spans="2:5" ht="21" x14ac:dyDescent="0.3">
-      <c r="B18" s="122" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="59" t="s">
+      <c r="E19" s="60" t="s">
         <v>53</v>
-      </c>
-      <c r="E19" s="60" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
@@ -4383,24 +4640,24 @@
       <c r="B3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="121" t="s">
+      <c r="C3" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="121"/>
-      <c r="F3" s="120" t="s">
+      <c r="D3" s="129"/>
+      <c r="F3" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
     </row>
     <row r="4" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="121"/>
+      <c r="D4" s="129"/>
       <c r="F4" s="35" t="s">
         <v>8</v>
       </c>
@@ -4410,10 +4667,10 @@
       <c r="B5" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="121" t="s">
+      <c r="C5" s="129" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="121"/>
+      <c r="D5" s="129"/>
       <c r="F5" s="35" t="s">
         <v>11</v>
       </c>
@@ -4423,10 +4680,10 @@
       <c r="B6" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="121" t="s">
+      <c r="C6" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="121"/>
+      <c r="D6" s="129"/>
       <c r="F6" s="36" t="s">
         <v>14</v>
       </c>
@@ -4436,10 +4693,10 @@
       <c r="B7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="121" t="s">
+      <c r="C7" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="121"/>
+      <c r="D7" s="129"/>
       <c r="F7" s="34" t="s">
         <v>17</v>
       </c>
@@ -4449,46 +4706,46 @@
       <c r="B8" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="121" t="s">
+      <c r="C8" s="129" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="121"/>
+      <c r="D8" s="129"/>
     </row>
     <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="121" t="s">
+      <c r="C9" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="121"/>
+      <c r="D9" s="129"/>
     </row>
     <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="121" t="s">
+      <c r="C10" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="121"/>
+      <c r="D10" s="129"/>
     </row>
     <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="121" t="s">
+      <c r="C11" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="121"/>
+      <c r="D11" s="129"/>
     </row>
     <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="121" t="s">
+      <c r="C12" s="129" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="121"/>
+      <c r="D12" s="129"/>
     </row>
     <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="41"/>
@@ -4498,27 +4755,32 @@
       <c r="B14" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="121" t="s">
+      <c r="C14" s="129" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="121"/>
+      <c r="D14" s="129"/>
     </row>
     <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="40"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
+      <c r="C15" s="129"/>
+      <c r="D15" s="129"/>
     </row>
     <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="121" t="s">
+      <c r="C16" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="121"/>
+      <c r="D16" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
@@ -4528,42 +4790,18 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
-    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4839,28 +5077,37 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
+    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4886,9 +5133,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/assets/files/Audit_Workpaper_Template.xlsx
+++ b/assets/files/Audit_Workpaper_Template.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2254" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD33A260-FEE7-410B-8252-231157B86D56}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="1116" windowWidth="29772" windowHeight="22392" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="23232" windowHeight="25296" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Detailed Results 2" sheetId="5" r:id="rId1"/>
@@ -1819,24 +1819,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="44" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -1851,6 +1835,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1860,12 +1853,42 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1878,24 +1901,6 @@
     <xf numFmtId="0" fontId="2" fillId="34" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1915,19 +1920,14 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="44" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2526,14 +2526,14 @@
   <sheetData>
     <row r="1" spans="2:20" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:20" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -2551,13 +2551,13 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="100" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="109"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="108"/>
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
       <c r="J4" s="13"/>
@@ -2567,13 +2567,13 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="111" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="109"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="108"/>
       <c r="H5" s="55"/>
       <c r="I5" s="55"/>
       <c r="J5" s="12"/>
@@ -2583,13 +2583,13 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="100" t="s">
+      <c r="B6" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="101"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="109"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="108"/>
       <c r="H6" s="55"/>
       <c r="I6" s="55"/>
       <c r="J6" s="12"/>
@@ -2623,9 +2623,9 @@
         <v>1</v>
       </c>
       <c r="C10" s="77"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="99"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="105"/>
       <c r="H10" s="23"/>
     </row>
     <row r="11" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2633,9 +2633,9 @@
         <v>2</v>
       </c>
       <c r="C11" s="77"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="99"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="105"/>
       <c r="H11" s="23"/>
     </row>
     <row r="12" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2643,9 +2643,9 @@
         <v>3</v>
       </c>
       <c r="C12" s="77"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="99"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="105"/>
       <c r="H12" s="23"/>
     </row>
     <row r="13" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2653,9 +2653,9 @@
         <v>4</v>
       </c>
       <c r="C13" s="77"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="99"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="105"/>
       <c r="H13" s="23"/>
     </row>
     <row r="14" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2663,9 +2663,9 @@
         <v>5</v>
       </c>
       <c r="C14" s="77"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="99"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="105"/>
       <c r="H14" s="23"/>
     </row>
     <row r="15" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2689,13 +2689,13 @@
       <c r="B17" s="1"/>
       <c r="F17" s="57"/>
       <c r="G17" s="57"/>
-      <c r="H17" s="106" t="s">
+      <c r="H17" s="102" t="s">
         <v>56</v>
       </c>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="102"/>
+      <c r="K17" s="102"/>
+      <c r="L17" s="102"/>
     </row>
     <row r="18" spans="2:14" s="30" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="15" t="s">
@@ -3199,11 +3199,11 @@
       <c r="B50" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="97" t="s">
+      <c r="C50" s="103" t="s">
         <v>68</v>
       </c>
-      <c r="D50" s="98"/>
-      <c r="E50" s="99"/>
+      <c r="D50" s="104"/>
+      <c r="E50" s="105"/>
       <c r="G50" s="68" t="s">
         <v>48</v>
       </c>
@@ -3232,11 +3232,11 @@
       <c r="B51" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="97" t="s">
+      <c r="C51" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="D51" s="98"/>
-      <c r="E51" s="99"/>
+      <c r="D51" s="104"/>
+      <c r="E51" s="105"/>
       <c r="G51" s="69" t="s">
         <v>67</v>
       </c>
@@ -3263,9 +3263,9 @@
     </row>
     <row r="52" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B52" s="54"/>
-      <c r="C52" s="97"/>
-      <c r="D52" s="98"/>
-      <c r="E52" s="99"/>
+      <c r="C52" s="103"/>
+      <c r="D52" s="104"/>
+      <c r="E52" s="105"/>
       <c r="G52" s="70"/>
       <c r="H52" s="71" t="str">
         <f t="shared" ref="H52:L55" si="1">_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G52), IF(_xlpm.x=0, "", _xlpm.x))</f>
@@ -3365,6 +3365,11 @@
     <row r="61" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="H17:L17"/>
@@ -3376,11 +3381,6 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3412,14 +3412,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3439,13 +3439,13 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="111"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="109"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="108"/>
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
       <c r="J4" s="13"/>
@@ -3456,13 +3456,13 @@
       <c r="U4" s="2"/>
     </row>
     <row r="5" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="113" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="111"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="109"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="108"/>
       <c r="H5" s="55"/>
       <c r="I5" s="55"/>
       <c r="J5" s="13"/>
@@ -3511,45 +3511,45 @@
     <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="52"/>
       <c r="C10" s="53"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="99"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="105"/>
       <c r="H10" s="23"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="52"/>
       <c r="C11" s="53"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="99"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="105"/>
       <c r="H11" s="23"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="52"/>
       <c r="C12" s="53"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="99"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="105"/>
       <c r="H12" s="23"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="52"/>
       <c r="C13" s="53"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="99"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="105"/>
       <c r="H13" s="23"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="52"/>
       <c r="C14" s="53"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="99"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="105"/>
       <c r="H14" s="23"/>
       <c r="N14" s="14"/>
     </row>
@@ -3586,25 +3586,25 @@
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="54"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="99"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="105"/>
       <c r="H18" s="23"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="54"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="99"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="105"/>
       <c r="H19" s="23"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="54"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="99"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="105"/>
       <c r="H20" s="23"/>
       <c r="N20" s="14"/>
     </row>
@@ -3644,252 +3644,257 @@
       <c r="N23" s="14"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C25" s="131"/>
-      <c r="D25" s="131"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="131"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="131"/>
-      <c r="I25" s="131"/>
+      <c r="C25" s="97"/>
+      <c r="D25" s="97"/>
+      <c r="E25" s="97"/>
+      <c r="F25" s="97"/>
+      <c r="G25" s="97"/>
+      <c r="H25" s="97"/>
+      <c r="I25" s="97"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C26" s="132"/>
-      <c r="D26" s="131"/>
-      <c r="E26" s="131"/>
-      <c r="F26" s="131"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="131"/>
-      <c r="I26" s="131"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="97"/>
+      <c r="E26" s="97"/>
+      <c r="F26" s="97"/>
+      <c r="G26" s="97"/>
+      <c r="H26" s="97"/>
+      <c r="I26" s="97"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C27" s="131"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="131"/>
+      <c r="C27" s="97"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="97"/>
+      <c r="F27" s="97"/>
+      <c r="G27" s="97"/>
+      <c r="H27" s="97"/>
+      <c r="I27" s="97"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C28" s="131"/>
-      <c r="D28" s="131"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="131"/>
-      <c r="G28" s="131"/>
-      <c r="H28" s="131"/>
-      <c r="I28" s="131"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="97"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C29" s="131"/>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="131"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="131"/>
-      <c r="I29" s="131"/>
+      <c r="C29" s="97"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="97"/>
+      <c r="F29" s="97"/>
+      <c r="G29" s="97"/>
+      <c r="H29" s="97"/>
+      <c r="I29" s="97"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C30" s="131"/>
-      <c r="D30" s="131"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="131"/>
-      <c r="G30" s="131"/>
-      <c r="H30" s="131"/>
-      <c r="I30" s="131"/>
+      <c r="C30" s="97"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="97"/>
+      <c r="F30" s="97"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="97"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C31" s="131"/>
-      <c r="D31" s="131"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="131"/>
-      <c r="G31" s="131"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="131"/>
+      <c r="C31" s="97"/>
+      <c r="D31" s="97"/>
+      <c r="E31" s="97"/>
+      <c r="F31" s="97"/>
+      <c r="G31" s="97"/>
+      <c r="H31" s="97"/>
+      <c r="I31" s="97"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C32" s="131"/>
-      <c r="D32" s="131"/>
-      <c r="E32" s="131"/>
-      <c r="F32" s="131"/>
-      <c r="G32" s="131"/>
-      <c r="H32" s="131"/>
-      <c r="I32" s="131"/>
+      <c r="C32" s="97"/>
+      <c r="D32" s="97"/>
+      <c r="E32" s="97"/>
+      <c r="F32" s="97"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="97"/>
+      <c r="I32" s="97"/>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="131"/>
-      <c r="D33" s="131"/>
-      <c r="E33" s="131"/>
-      <c r="F33" s="131"/>
-      <c r="G33" s="131"/>
-      <c r="H33" s="131"/>
-      <c r="I33" s="131"/>
+      <c r="C33" s="97"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="97"/>
+      <c r="G33" s="97"/>
+      <c r="H33" s="97"/>
+      <c r="I33" s="97"/>
     </row>
     <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="131"/>
-      <c r="D34" s="131"/>
-      <c r="E34" s="131"/>
-      <c r="F34" s="131"/>
-      <c r="G34" s="131"/>
-      <c r="H34" s="131"/>
-      <c r="I34" s="131"/>
+      <c r="C34" s="97"/>
+      <c r="D34" s="97"/>
+      <c r="E34" s="97"/>
+      <c r="F34" s="97"/>
+      <c r="G34" s="97"/>
+      <c r="H34" s="97"/>
+      <c r="I34" s="97"/>
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C35" s="131"/>
-      <c r="D35" s="131"/>
-      <c r="E35" s="131"/>
-      <c r="F35" s="131"/>
-      <c r="G35" s="131"/>
-      <c r="H35" s="131"/>
-      <c r="I35" s="131"/>
+      <c r="C35" s="97"/>
+      <c r="D35" s="97"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="97"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="97"/>
+      <c r="I35" s="97"/>
     </row>
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C36" s="131"/>
-      <c r="D36" s="133" t="s">
+      <c r="C36" s="97"/>
+      <c r="D36" s="112" t="s">
         <v>70</v>
       </c>
-      <c r="E36" s="133"/>
-      <c r="F36" s="133"/>
-      <c r="G36" s="133"/>
-      <c r="H36" s="131"/>
-      <c r="I36" s="131"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="112"/>
+      <c r="H36" s="97"/>
+      <c r="I36" s="97"/>
     </row>
     <row r="37" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C37" s="131"/>
-      <c r="D37" s="131"/>
-      <c r="E37" s="131"/>
-      <c r="F37" s="131"/>
-      <c r="G37" s="131"/>
-      <c r="H37" s="131"/>
-      <c r="I37" s="131"/>
+      <c r="C37" s="97"/>
+      <c r="D37" s="97"/>
+      <c r="E37" s="97"/>
+      <c r="F37" s="97"/>
+      <c r="G37" s="97"/>
+      <c r="H37" s="97"/>
+      <c r="I37" s="97"/>
     </row>
     <row r="38" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C38" s="131"/>
-      <c r="D38" s="131"/>
-      <c r="E38" s="131"/>
-      <c r="F38" s="131"/>
-      <c r="G38" s="131"/>
-      <c r="H38" s="131"/>
-      <c r="I38" s="131"/>
+      <c r="C38" s="97"/>
+      <c r="D38" s="97"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="97"/>
+      <c r="G38" s="97"/>
+      <c r="H38" s="97"/>
+      <c r="I38" s="97"/>
     </row>
     <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C39" s="131"/>
-      <c r="D39" s="131"/>
-      <c r="E39" s="131"/>
-      <c r="F39" s="131"/>
-      <c r="G39" s="131"/>
-      <c r="H39" s="131"/>
-      <c r="I39" s="131"/>
+      <c r="C39" s="97"/>
+      <c r="D39" s="97"/>
+      <c r="E39" s="97"/>
+      <c r="F39" s="97"/>
+      <c r="G39" s="97"/>
+      <c r="H39" s="97"/>
+      <c r="I39" s="97"/>
     </row>
     <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C40" s="131"/>
-      <c r="D40" s="131"/>
-      <c r="E40" s="131"/>
-      <c r="F40" s="131"/>
-      <c r="G40" s="131"/>
-      <c r="H40" s="131"/>
-      <c r="I40" s="131"/>
+      <c r="C40" s="97"/>
+      <c r="D40" s="97"/>
+      <c r="E40" s="97"/>
+      <c r="F40" s="97"/>
+      <c r="G40" s="97"/>
+      <c r="H40" s="97"/>
+      <c r="I40" s="97"/>
     </row>
     <row r="41" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C41" s="131"/>
-      <c r="D41" s="131"/>
-      <c r="E41" s="131"/>
-      <c r="F41" s="131"/>
-      <c r="G41" s="131"/>
-      <c r="H41" s="131"/>
-      <c r="I41" s="131"/>
+      <c r="C41" s="97"/>
+      <c r="D41" s="97"/>
+      <c r="E41" s="97"/>
+      <c r="F41" s="97"/>
+      <c r="G41" s="97"/>
+      <c r="H41" s="97"/>
+      <c r="I41" s="97"/>
     </row>
     <row r="42" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C42" s="131"/>
-      <c r="D42" s="131"/>
-      <c r="E42" s="131"/>
-      <c r="F42" s="131"/>
-      <c r="G42" s="131"/>
-      <c r="H42" s="131"/>
-      <c r="I42" s="131"/>
+      <c r="C42" s="97"/>
+      <c r="D42" s="97"/>
+      <c r="E42" s="97"/>
+      <c r="F42" s="97"/>
+      <c r="G42" s="97"/>
+      <c r="H42" s="97"/>
+      <c r="I42" s="97"/>
     </row>
     <row r="43" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C43" s="131"/>
-      <c r="D43" s="131"/>
-      <c r="E43" s="131"/>
-      <c r="F43" s="131"/>
-      <c r="G43" s="131"/>
-      <c r="H43" s="131"/>
-      <c r="I43" s="131"/>
+      <c r="C43" s="97"/>
+      <c r="D43" s="97"/>
+      <c r="E43" s="97"/>
+      <c r="F43" s="97"/>
+      <c r="G43" s="97"/>
+      <c r="H43" s="97"/>
+      <c r="I43" s="97"/>
     </row>
     <row r="44" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C44" s="131"/>
-      <c r="D44" s="131"/>
-      <c r="E44" s="131"/>
-      <c r="F44" s="131"/>
-      <c r="G44" s="131"/>
-      <c r="H44" s="131"/>
-      <c r="I44" s="131"/>
+      <c r="C44" s="97"/>
+      <c r="D44" s="97"/>
+      <c r="E44" s="97"/>
+      <c r="F44" s="97"/>
+      <c r="G44" s="97"/>
+      <c r="H44" s="97"/>
+      <c r="I44" s="97"/>
     </row>
     <row r="45" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C45" s="131"/>
-      <c r="D45" s="131"/>
-      <c r="E45" s="131"/>
-      <c r="F45" s="131"/>
-      <c r="G45" s="131"/>
-      <c r="H45" s="131"/>
-      <c r="I45" s="131"/>
+      <c r="C45" s="97"/>
+      <c r="D45" s="97"/>
+      <c r="E45" s="97"/>
+      <c r="F45" s="97"/>
+      <c r="G45" s="97"/>
+      <c r="H45" s="97"/>
+      <c r="I45" s="97"/>
     </row>
     <row r="46" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C46" s="131"/>
-      <c r="D46" s="131"/>
-      <c r="E46" s="131"/>
-      <c r="F46" s="131"/>
-      <c r="G46" s="131"/>
-      <c r="H46" s="131"/>
-      <c r="I46" s="131"/>
+      <c r="C46" s="97"/>
+      <c r="D46" s="97"/>
+      <c r="E46" s="97"/>
+      <c r="F46" s="97"/>
+      <c r="G46" s="97"/>
+      <c r="H46" s="97"/>
+      <c r="I46" s="97"/>
     </row>
     <row r="47" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C47" s="131"/>
-      <c r="D47" s="131"/>
-      <c r="E47" s="131"/>
-      <c r="F47" s="131"/>
-      <c r="G47" s="131"/>
-      <c r="H47" s="131"/>
-      <c r="I47" s="131"/>
+      <c r="C47" s="97"/>
+      <c r="D47" s="97"/>
+      <c r="E47" s="97"/>
+      <c r="F47" s="97"/>
+      <c r="G47" s="97"/>
+      <c r="H47" s="97"/>
+      <c r="I47" s="97"/>
     </row>
     <row r="48" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C48" s="131"/>
-      <c r="D48" s="131"/>
-      <c r="E48" s="131"/>
-      <c r="F48" s="131"/>
-      <c r="G48" s="131"/>
-      <c r="H48" s="131"/>
-      <c r="I48" s="131"/>
+      <c r="C48" s="97"/>
+      <c r="D48" s="97"/>
+      <c r="E48" s="97"/>
+      <c r="F48" s="97"/>
+      <c r="G48" s="97"/>
+      <c r="H48" s="97"/>
+      <c r="I48" s="97"/>
     </row>
     <row r="49" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C49" s="131"/>
-      <c r="D49" s="131"/>
-      <c r="E49" s="131"/>
-      <c r="F49" s="131"/>
-      <c r="G49" s="131"/>
-      <c r="H49" s="131"/>
-      <c r="I49" s="131"/>
+      <c r="C49" s="97"/>
+      <c r="D49" s="97"/>
+      <c r="E49" s="97"/>
+      <c r="F49" s="97"/>
+      <c r="G49" s="97"/>
+      <c r="H49" s="97"/>
+      <c r="I49" s="97"/>
     </row>
     <row r="50" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C50" s="131"/>
-      <c r="D50" s="131"/>
-      <c r="E50" s="131"/>
-      <c r="F50" s="131"/>
-      <c r="G50" s="131"/>
-      <c r="H50" s="131"/>
-      <c r="I50" s="131"/>
+      <c r="C50" s="97"/>
+      <c r="D50" s="97"/>
+      <c r="E50" s="97"/>
+      <c r="F50" s="97"/>
+      <c r="G50" s="97"/>
+      <c r="H50" s="97"/>
+      <c r="I50" s="97"/>
     </row>
     <row r="51" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C51" s="131"/>
-      <c r="D51" s="131"/>
-      <c r="E51" s="131"/>
-      <c r="F51" s="131"/>
-      <c r="G51" s="131"/>
-      <c r="H51" s="131"/>
-      <c r="I51" s="131"/>
+      <c r="C51" s="97"/>
+      <c r="D51" s="97"/>
+      <c r="E51" s="97"/>
+      <c r="F51" s="97"/>
+      <c r="G51" s="97"/>
+      <c r="H51" s="97"/>
+      <c r="I51" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="D36:G36"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="D4:F4"/>
@@ -3899,11 +3904,6 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3935,14 +3935,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3962,22 +3962,22 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="111"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="109"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="108"/>
     </row>
     <row r="5" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="113" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="111"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="109"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="108"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
@@ -4011,45 +4011,45 @@
     <row r="10" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="52"/>
       <c r="C10" s="53"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="99"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="105"/>
       <c r="H10" s="23"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="52"/>
       <c r="C11" s="53"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="99"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="105"/>
       <c r="H11" s="23"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="52"/>
       <c r="C12" s="53"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="99"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="105"/>
       <c r="H12" s="23"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B13" s="52"/>
       <c r="C13" s="53"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="99"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="105"/>
       <c r="H13" s="23"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B14" s="52"/>
       <c r="C14" s="53"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="99"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="105"/>
       <c r="H14" s="23"/>
       <c r="N14" s="14"/>
     </row>
@@ -4086,25 +4086,25 @@
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="54"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="99"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="105"/>
       <c r="H18" s="23"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B19" s="54"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="99"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="105"/>
       <c r="H19" s="23"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B20" s="54"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="99"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="105"/>
       <c r="H20" s="23"/>
       <c r="N20" s="14"/>
     </row>
@@ -4138,11 +4138,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D12:F12"/>
@@ -4151,6 +4146,11 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4171,43 +4171,43 @@
     <row r="3" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="111"/>
-      <c r="D5" s="112"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="123"/>
     </row>
     <row r="6" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="115" t="s">
+      <c r="B6" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="115"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="113"/>
-      <c r="J6" s="114"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="123"/>
     </row>
     <row r="7" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="100" t="s">
+      <c r="B7" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="100"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="109"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="108"/>
     </row>
     <row r="9" spans="2:10" ht="21" x14ac:dyDescent="0.3">
       <c r="B9" s="91" t="s">
@@ -4220,15 +4220,15 @@
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="119"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="121"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="14"/>
@@ -4242,15 +4242,15 @@
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="119"/>
-      <c r="C14" s="120"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="120"/>
-      <c r="J14" s="121"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="16" spans="2:10" ht="18" x14ac:dyDescent="0.35">
       <c r="B16" s="92" t="s">
@@ -4258,15 +4258,15 @@
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="119"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="121"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="50"/>
@@ -4283,15 +4283,15 @@
       <c r="E19" s="50"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="119"/>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="120"/>
-      <c r="J20" s="121"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="120"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="14"/>
@@ -4308,15 +4308,15 @@
       <c r="E22" s="14"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="119"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="120"/>
-      <c r="E23" s="120"/>
-      <c r="F23" s="120"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="120"/>
-      <c r="I23" s="120"/>
-      <c r="J23" s="121"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="120"/>
     </row>
     <row r="25" spans="2:10" ht="21" x14ac:dyDescent="0.3">
       <c r="B25" s="88" t="s">
@@ -4333,30 +4333,30 @@
     </row>
     <row r="27" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B27" s="56"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="117"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="117"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="118"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="117"/>
     </row>
     <row r="28" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B28" s="56"/>
-      <c r="C28" s="116"/>
-      <c r="D28" s="117"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="117"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="118"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="116"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="116"/>
+      <c r="G28" s="116"/>
+      <c r="H28" s="117"/>
     </row>
     <row r="29" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B29" s="56"/>
-      <c r="C29" s="97"/>
-      <c r="D29" s="98"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="98"/>
-      <c r="G29" s="98"/>
-      <c r="H29" s="99"/>
+      <c r="C29" s="103"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="105"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="8"/>
@@ -4368,6 +4368,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:J7"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="B11:J11"/>
@@ -4376,12 +4382,6 @@
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="C27:H27"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4414,14 +4414,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -4441,12 +4441,12 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="128" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="126"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="128"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="131"/>
       <c r="G4" s="57"/>
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
@@ -4477,9 +4477,9 @@
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="95"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="124"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="127"/>
       <c r="G7" s="57"/>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.3">
@@ -4493,9 +4493,9 @@
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B10" s="96"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="124"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="126"/>
+      <c r="E10" s="127"/>
       <c r="G10" s="57"/>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.3">
@@ -4508,9 +4508,9 @@
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B13" s="96"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="124"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="127"/>
       <c r="G13" s="57"/>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.3">
@@ -4523,9 +4523,9 @@
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B16" s="96"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="124"/>
+      <c r="C16" s="125"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="127"/>
       <c r="G16" s="57"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
@@ -4640,24 +4640,24 @@
       <c r="B3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="129" t="s">
+      <c r="C3" s="133" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="129"/>
-      <c r="F3" s="130" t="s">
+      <c r="D3" s="133"/>
+      <c r="F3" s="132" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="132"/>
     </row>
     <row r="4" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="129" t="s">
+      <c r="C4" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="129"/>
+      <c r="D4" s="133"/>
       <c r="F4" s="35" t="s">
         <v>8</v>
       </c>
@@ -4667,10 +4667,10 @@
       <c r="B5" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="129" t="s">
+      <c r="C5" s="133" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="129"/>
+      <c r="D5" s="133"/>
       <c r="F5" s="35" t="s">
         <v>11</v>
       </c>
@@ -4680,10 +4680,10 @@
       <c r="B6" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="129" t="s">
+      <c r="C6" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="129"/>
+      <c r="D6" s="133"/>
       <c r="F6" s="36" t="s">
         <v>14</v>
       </c>
@@ -4693,10 +4693,10 @@
       <c r="B7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="129"/>
+      <c r="D7" s="133"/>
       <c r="F7" s="34" t="s">
         <v>17</v>
       </c>
@@ -4706,46 +4706,46 @@
       <c r="B8" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="129" t="s">
+      <c r="C8" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="129"/>
+      <c r="D8" s="133"/>
     </row>
     <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="129" t="s">
+      <c r="C9" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="129"/>
+      <c r="D9" s="133"/>
     </row>
     <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="129" t="s">
+      <c r="C10" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="129"/>
+      <c r="D10" s="133"/>
     </row>
     <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="129" t="s">
+      <c r="C11" s="133" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="129"/>
+      <c r="D11" s="133"/>
     </row>
     <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="129" t="s">
+      <c r="C12" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="129"/>
+      <c r="D12" s="133"/>
     </row>
     <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="41"/>
@@ -4755,32 +4755,27 @@
       <c r="B14" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="129" t="s">
+      <c r="C14" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="129"/>
+      <c r="D14" s="133"/>
     </row>
     <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="40"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
     </row>
     <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="129" t="s">
+      <c r="C16" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="129"/>
+      <c r="D16" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
@@ -4790,18 +4785,42 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
+    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5077,37 +5096,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
-    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5133,19 +5143,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/assets/files/Audit_Workpaper_Template.xlsx
+++ b/assets/files/Audit_Workpaper_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fjmgt-my.sharepoint.com/personal/colby_kellersberger_fjmgt_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\colby\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2254" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD33A260-FEE7-410B-8252-231157B86D56}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D9AE7F-5683-4117-9880-1F038C859525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="23232" windowHeight="25296" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5025" yWindow="5025" windowWidth="38700" windowHeight="15345" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Detailed Results 2" sheetId="5" r:id="rId1"/>
@@ -20,14 +20,6 @@
     <sheet name="Planning Document" sheetId="7" r:id="rId5"/>
     <sheet name="Instructions _ Common Tickmarks" sheetId="2" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="NoYes">'[1]Drop down'!$Q$6:$Q$7</definedName>
-    <definedName name="sdsd">'[2]Drop down'!$Q$6:$Q$7</definedName>
-  </definedNames>
   <calcPr calcId="191028" concurrentCalc="0" concurrentManualCount="20"/>
   <fileRecoveryPr autoRecover="0"/>
   <extLst>
@@ -1821,6 +1813,24 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="44" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -1835,15 +1845,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1853,23 +1854,26 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1889,18 +1893,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1920,14 +1912,14 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1996,218 +1988,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Scoping"/>
-      <sheetName val="Master Review Procedures"/>
-      <sheetName val="Master Review Procedures (4)"/>
-      <sheetName val="Master Review Procedures (7)"/>
-      <sheetName val="Master Review Procedures (16)"/>
-      <sheetName val="First Test Plan"/>
-      <sheetName val="Master Test Plan"/>
-      <sheetName val="Control Activity-1"/>
-      <sheetName val="Control Activity-2"/>
-      <sheetName val="Master Control Activity"/>
-      <sheetName val="Master Follow-Up Items"/>
-      <sheetName val="Master Testing Table Review"/>
-      <sheetName val="Master Procedures (1)"/>
-      <sheetName val="Library Procedures"/>
-      <sheetName val="Master Procedures (2)"/>
-      <sheetName val="Master Procedures (3)"/>
-      <sheetName val="Master Procedures (4)"/>
-      <sheetName val="Master Procedures (5)"/>
-      <sheetName val="Master Procedures (6)"/>
-      <sheetName val="Master Procedures (7)"/>
-      <sheetName val="Master Procedures (8)"/>
-      <sheetName val="Master Procedures (9)"/>
-      <sheetName val="Master Procedures (10)"/>
-      <sheetName val="Master Procedures (11)"/>
-      <sheetName val="Master Procedures (12)"/>
-      <sheetName val="Master Procedures (13)"/>
-      <sheetName val="Master Procedures (14)"/>
-      <sheetName val="Master Procedures (15)"/>
-      <sheetName val="Master Procedures (16)"/>
-      <sheetName val="Master Procedures (CUST)"/>
-      <sheetName val="Master Procedures (CUST_PCAOB)"/>
-      <sheetName val="Master ToC Template"/>
-      <sheetName val="Master ToC Template US"/>
-      <sheetName val="ToC Template"/>
-      <sheetName val="Master Testing Table"/>
-      <sheetName val="Master Testing Table US"/>
-      <sheetName val="Testing Table"/>
-      <sheetName val="Master Update"/>
-      <sheetName val="Master PAE_NonUS"/>
-      <sheetName val="Master PAE_AICPA"/>
-      <sheetName val="Master PAE_PCAOB"/>
-      <sheetName val="Drop down"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41">
-        <row r="6">
-          <cell r="Q6" t="str">
-            <v>No</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="Q7" t="str">
-            <v>Yes</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Scoping"/>
-      <sheetName val="Master Review Procedures"/>
-      <sheetName val="Master Review Procedures (4)"/>
-      <sheetName val="Master Review Procedures (7)"/>
-      <sheetName val="Master Review Procedures (16)"/>
-      <sheetName val="First Test Plan"/>
-      <sheetName val="Master Test Plan"/>
-      <sheetName val="Control Activity-1"/>
-      <sheetName val="Control Activity-2"/>
-      <sheetName val="Master Control Activity"/>
-      <sheetName val="Master Follow-Up Items"/>
-      <sheetName val="Master Testing Table Review"/>
-      <sheetName val="Master Procedures (1)"/>
-      <sheetName val="Library Procedures"/>
-      <sheetName val="Master Procedures (2)"/>
-      <sheetName val="Master Procedures (3)"/>
-      <sheetName val="Master Procedures (4)"/>
-      <sheetName val="Master Procedures (5)"/>
-      <sheetName val="Master Procedures (6)"/>
-      <sheetName val="Master Procedures (7)"/>
-      <sheetName val="Master Procedures (8)"/>
-      <sheetName val="Master Procedures (9)"/>
-      <sheetName val="Master Procedures (10)"/>
-      <sheetName val="Master Procedures (11)"/>
-      <sheetName val="Master Procedures (12)"/>
-      <sheetName val="Master Procedures (13)"/>
-      <sheetName val="Master Procedures (14)"/>
-      <sheetName val="Master Procedures (15)"/>
-      <sheetName val="Master Procedures (16)"/>
-      <sheetName val="Master Procedures (CUST)"/>
-      <sheetName val="Master Procedures (CUST_PCAOB)"/>
-      <sheetName val="Master ToC Template"/>
-      <sheetName val="Master ToC Template US"/>
-      <sheetName val="ToC Template"/>
-      <sheetName val="Master Testing Table"/>
-      <sheetName val="Master Testing Table US"/>
-      <sheetName val="Testing Table"/>
-      <sheetName val="Master Update"/>
-      <sheetName val="Master PAE_NonUS"/>
-      <sheetName val="Master PAE_AICPA"/>
-      <sheetName val="Master PAE_PCAOB"/>
-      <sheetName val="Drop down"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41">
-        <row r="6">
-          <cell r="Q6" t="str">
-            <v>No</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="Q7" t="str">
-            <v>Yes</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2509,36 +2289,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD103B3-4618-405C-A46A-99E8E6568320}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B1:T61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.5546875" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="27.109375" customWidth="1"/>
-    <col min="5" max="5" width="23.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="29.88671875" style="14" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="29.85546875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:20" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
+    <row r="1" spans="2:20" ht="7.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:20" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
     </row>
-    <row r="3" spans="2:20" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:20" ht="5.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -2550,14 +2330,14 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="100" t="s">
+    <row r="4" spans="2:20" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="108"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="111"/>
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
       <c r="J4" s="13"/>
@@ -2566,14 +2346,14 @@
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="111" t="s">
+    <row r="5" spans="2:20" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="109"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="108"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="111"/>
       <c r="H5" s="55"/>
       <c r="I5" s="55"/>
       <c r="J5" s="12"/>
@@ -2582,14 +2362,14 @@
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="109" t="s">
+    <row r="6" spans="2:20" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="110"/>
-      <c r="D6" s="106"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="108"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="111"/>
       <c r="H6" s="55"/>
       <c r="I6" s="55"/>
       <c r="J6" s="12"/>
@@ -2598,14 +2378,14 @@
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
     </row>
-    <row r="8" spans="2:20" ht="21" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:20" ht="21" x14ac:dyDescent="0.25">
       <c r="B8" s="84" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
     </row>
-    <row r="9" spans="2:20" ht="21" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:20" ht="21" x14ac:dyDescent="0.25">
       <c r="B9" s="85" t="s">
         <v>35</v>
       </c>
@@ -2618,57 +2398,57 @@
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
     </row>
-    <row r="10" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="52">
         <v>1</v>
       </c>
       <c r="C10" s="77"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="105"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="101"/>
       <c r="H10" s="23"/>
     </row>
-    <row r="11" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="52">
         <v>2</v>
       </c>
       <c r="C11" s="77"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="105"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="101"/>
       <c r="H11" s="23"/>
     </row>
-    <row r="12" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="52">
         <v>3</v>
       </c>
       <c r="C12" s="77"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="105"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="101"/>
       <c r="H12" s="23"/>
     </row>
-    <row r="13" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="52">
         <v>4</v>
       </c>
       <c r="C13" s="77"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="105"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="101"/>
       <c r="H13" s="23"/>
     </row>
-    <row r="14" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="52">
         <v>5</v>
       </c>
       <c r="C14" s="77"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="105"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="101"/>
       <c r="H14" s="23"/>
     </row>
-    <row r="15" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="52"/>
       <c r="C15" s="75"/>
       <c r="D15" s="75"/>
@@ -2676,7 +2456,7 @@
       <c r="F15" s="75"/>
       <c r="H15" s="23"/>
     </row>
-    <row r="16" spans="2:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="45"/>
       <c r="C16" s="48"/>
       <c r="D16" s="49"/>
@@ -2685,19 +2465,19 @@
       <c r="G16" s="23"/>
       <c r="H16" s="23"/>
     </row>
-    <row r="17" spans="2:14" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" ht="23.25" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="F17" s="57"/>
       <c r="G17" s="57"/>
-      <c r="H17" s="102" t="s">
+      <c r="H17" s="108" t="s">
         <v>56</v>
       </c>
-      <c r="I17" s="102"/>
-      <c r="J17" s="102"/>
-      <c r="K17" s="102"/>
-      <c r="L17" s="102"/>
-    </row>
-    <row r="18" spans="2:14" s="30" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I17" s="108"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
+    </row>
+    <row r="18" spans="2:14" s="30" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>39</v>
       </c>
@@ -2726,7 +2506,7 @@
       </c>
       <c r="N18" s="17"/>
     </row>
-    <row r="19" spans="2:14" s="3" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" s="3" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B19" s="24">
         <v>1</v>
       </c>
@@ -2746,7 +2526,7 @@
       <c r="L19" s="78"/>
       <c r="M19" s="32"/>
     </row>
-    <row r="20" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="24">
         <v>2</v>
       </c>
@@ -2762,7 +2542,7 @@
       <c r="L20" s="22"/>
       <c r="M20" s="32"/>
     </row>
-    <row r="21" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="24">
         <v>3</v>
       </c>
@@ -2778,7 +2558,7 @@
       <c r="L21" s="22"/>
       <c r="M21" s="32"/>
     </row>
-    <row r="22" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="24">
         <v>4</v>
       </c>
@@ -2794,7 +2574,7 @@
       <c r="L22" s="22"/>
       <c r="M22" s="32"/>
     </row>
-    <row r="23" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="24">
         <v>5</v>
       </c>
@@ -2810,7 +2590,7 @@
       <c r="L23" s="22"/>
       <c r="M23" s="32"/>
     </row>
-    <row r="24" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="24">
         <v>6</v>
       </c>
@@ -2826,7 +2606,7 @@
       <c r="L24" s="22"/>
       <c r="M24" s="32"/>
     </row>
-    <row r="25" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="24">
         <v>7</v>
       </c>
@@ -2842,7 +2622,7 @@
       <c r="L25" s="22"/>
       <c r="M25" s="32"/>
     </row>
-    <row r="26" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="24">
         <v>8</v>
       </c>
@@ -2858,7 +2638,7 @@
       <c r="L26" s="22"/>
       <c r="M26" s="32"/>
     </row>
-    <row r="27" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="24">
         <v>9</v>
       </c>
@@ -2874,7 +2654,7 @@
       <c r="L27" s="22"/>
       <c r="M27" s="32"/>
     </row>
-    <row r="28" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="24">
         <v>10</v>
       </c>
@@ -2890,7 +2670,7 @@
       <c r="L28" s="22"/>
       <c r="M28" s="32"/>
     </row>
-    <row r="29" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="24">
         <v>11</v>
       </c>
@@ -2906,7 +2686,7 @@
       <c r="L29" s="22"/>
       <c r="M29" s="32"/>
     </row>
-    <row r="30" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="24">
         <v>12</v>
       </c>
@@ -2922,7 +2702,7 @@
       <c r="L30" s="22"/>
       <c r="M30" s="32"/>
     </row>
-    <row r="31" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="24">
         <v>13</v>
       </c>
@@ -2938,7 +2718,7 @@
       <c r="L31" s="22"/>
       <c r="M31" s="32"/>
     </row>
-    <row r="32" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="24">
         <v>14</v>
       </c>
@@ -2954,7 +2734,7 @@
       <c r="L32" s="22"/>
       <c r="M32" s="32"/>
     </row>
-    <row r="33" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="24">
         <v>15</v>
       </c>
@@ -2970,7 +2750,7 @@
       <c r="L33" s="22"/>
       <c r="M33" s="32"/>
     </row>
-    <row r="34" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="24">
         <v>16</v>
       </c>
@@ -2986,7 +2766,7 @@
       <c r="L34" s="22"/>
       <c r="M34" s="32"/>
     </row>
-    <row r="35" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="24">
         <v>17</v>
       </c>
@@ -3002,7 +2782,7 @@
       <c r="L35" s="22"/>
       <c r="M35" s="32"/>
     </row>
-    <row r="36" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="24">
         <v>18</v>
       </c>
@@ -3018,7 +2798,7 @@
       <c r="L36" s="22"/>
       <c r="M36" s="32"/>
     </row>
-    <row r="37" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="24">
         <v>19</v>
       </c>
@@ -3034,7 +2814,7 @@
       <c r="L37" s="22"/>
       <c r="M37" s="32"/>
     </row>
-    <row r="38" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="24">
         <v>20</v>
       </c>
@@ -3050,7 +2830,7 @@
       <c r="L38" s="22"/>
       <c r="M38" s="32"/>
     </row>
-    <row r="39" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="24">
         <v>21</v>
       </c>
@@ -3066,7 +2846,7 @@
       <c r="L39" s="22"/>
       <c r="M39" s="32"/>
     </row>
-    <row r="40" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="24">
         <v>22</v>
       </c>
@@ -3082,7 +2862,7 @@
       <c r="L40" s="22"/>
       <c r="M40" s="32"/>
     </row>
-    <row r="41" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="24">
         <v>23</v>
       </c>
@@ -3098,7 +2878,7 @@
       <c r="L41" s="22"/>
       <c r="M41" s="32"/>
     </row>
-    <row r="42" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="24">
         <v>24</v>
       </c>
@@ -3114,7 +2894,7 @@
       <c r="L42" s="22"/>
       <c r="M42" s="32"/>
     </row>
-    <row r="43" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="24">
         <v>25</v>
       </c>
@@ -3130,7 +2910,7 @@
       <c r="L43" s="22"/>
       <c r="M43" s="32"/>
     </row>
-    <row r="44" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="26"/>
@@ -3144,7 +2924,7 @@
       <c r="L44" s="29"/>
       <c r="M44" s="31"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -3157,10 +2937,10 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C47" s="51"/>
     </row>
-    <row r="48" spans="2:13" ht="21" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:13" ht="21" x14ac:dyDescent="0.35">
       <c r="B48" s="84" t="s">
         <v>55</v>
       </c>
@@ -3169,7 +2949,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="85" t="s">
         <v>35</v>
       </c>
@@ -3195,15 +2975,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B50" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="103" t="s">
+      <c r="C50" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="D50" s="104"/>
-      <c r="E50" s="105"/>
+      <c r="D50" s="100"/>
+      <c r="E50" s="101"/>
       <c r="G50" s="68" t="s">
         <v>48</v>
       </c>
@@ -3228,15 +3008,15 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B51" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="103" t="s">
+      <c r="C51" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="D51" s="104"/>
-      <c r="E51" s="105"/>
+      <c r="D51" s="100"/>
+      <c r="E51" s="101"/>
       <c r="G51" s="69" t="s">
         <v>67</v>
       </c>
@@ -3261,11 +3041,11 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B52" s="54"/>
-      <c r="C52" s="103"/>
-      <c r="D52" s="104"/>
-      <c r="E52" s="105"/>
+      <c r="C52" s="99"/>
+      <c r="D52" s="100"/>
+      <c r="E52" s="101"/>
       <c r="G52" s="70"/>
       <c r="H52" s="71" t="str">
         <f t="shared" ref="H52:L55" si="1">_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G52), IF(_xlpm.x=0, "", _xlpm.x))</f>
@@ -3288,7 +3068,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="2:12" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="G53" s="57"/>
       <c r="H53" s="71" t="str">
         <f t="shared" si="1"/>
@@ -3311,7 +3091,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:12" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="G54" s="57"/>
       <c r="H54" s="71" t="str">
         <f t="shared" si="1"/>
@@ -3334,7 +3114,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="2:12" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="G55" s="57"/>
       <c r="H55" s="71" t="str">
         <f t="shared" si="1"/>
@@ -3357,19 +3137,14 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H56" s="57"/>
     </row>
-    <row r="59" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="H17:L17"/>
@@ -3381,6 +3156,11 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3391,41 +3171,41 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C2776A-E04F-41FD-B3D7-35684437E078}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B1:U51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.5546875" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" customWidth="1"/>
-    <col min="4" max="4" width="27.109375" customWidth="1"/>
-    <col min="5" max="5" width="23.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="17.5546875" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:21" ht="11.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="8"/>
       <c r="N1" s="14"/>
     </row>
-    <row r="2" spans="2:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
+    <row r="2" spans="2:21" ht="11.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
       <c r="N2" s="14"/>
     </row>
-    <row r="3" spans="2:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:21" ht="11.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -3438,14 +3218,14 @@
       <c r="K3" s="1"/>
       <c r="N3" s="14"/>
     </row>
-    <row r="4" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="113" t="s">
+    <row r="4" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="114"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="108"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="111"/>
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
       <c r="J4" s="13"/>
@@ -3455,14 +3235,14 @@
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
     </row>
-    <row r="5" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="113" t="s">
+    <row r="5" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="108"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="111"/>
       <c r="H5" s="55"/>
       <c r="I5" s="55"/>
       <c r="J5" s="13"/>
@@ -3472,11 +3252,11 @@
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="N6" s="14"/>
     </row>
-    <row r="7" spans="2:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
@@ -3486,7 +3266,7 @@
       <c r="H7" s="23"/>
       <c r="N7" s="14"/>
     </row>
-    <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B8" s="88" t="s">
         <v>54</v>
       </c>
@@ -3494,7 +3274,7 @@
       <c r="H8" s="23"/>
       <c r="N8" s="14"/>
     </row>
-    <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B9" s="85" t="s">
         <v>35</v>
       </c>
@@ -3508,52 +3288,52 @@
       <c r="H9" s="23"/>
       <c r="N9" s="14"/>
     </row>
-    <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="52"/>
       <c r="C10" s="53"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="105"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="101"/>
       <c r="H10" s="23"/>
       <c r="N10" s="14"/>
     </row>
-    <row r="11" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="52"/>
       <c r="C11" s="53"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="105"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="101"/>
       <c r="H11" s="23"/>
       <c r="N11" s="14"/>
     </row>
-    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="52"/>
       <c r="C12" s="53"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="105"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="101"/>
       <c r="H12" s="23"/>
       <c r="N12" s="14"/>
     </row>
-    <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="52"/>
       <c r="C13" s="53"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="105"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="101"/>
       <c r="H13" s="23"/>
       <c r="N13" s="14"/>
     </row>
-    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="52"/>
       <c r="C14" s="53"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="105"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="101"/>
       <c r="H14" s="23"/>
       <c r="N14" s="14"/>
     </row>
-    <row r="15" spans="2:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="45"/>
       <c r="C15" s="48"/>
       <c r="D15" s="49"/>
@@ -3563,7 +3343,7 @@
       <c r="H15" s="23"/>
       <c r="N15" s="14"/>
     </row>
-    <row r="16" spans="2:21" ht="21" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B16" s="88" t="s">
         <v>55</v>
       </c>
@@ -3572,7 +3352,7 @@
       <c r="H16" s="23"/>
       <c r="N16" s="14"/>
     </row>
-    <row r="17" spans="2:14" ht="21" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B17" s="85" t="s">
         <v>35</v>
       </c>
@@ -3584,31 +3364,31 @@
       <c r="H17" s="23"/>
       <c r="N17" s="14"/>
     </row>
-    <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="54"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="105"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="101"/>
       <c r="H18" s="23"/>
       <c r="N18" s="14"/>
     </row>
-    <row r="19" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="54"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="105"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="101"/>
       <c r="H19" s="23"/>
       <c r="N19" s="14"/>
     </row>
-    <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="54"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="105"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="101"/>
       <c r="H20" s="23"/>
       <c r="N20" s="14"/>
     </row>
-    <row r="21" spans="2:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="45"/>
       <c r="C21" s="48"/>
       <c r="D21" s="49"/>
@@ -3618,7 +3398,7 @@
       <c r="H21" s="23"/>
       <c r="N21" s="14"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="18"/>
       <c r="C22" s="50"/>
       <c r="D22" s="50"/>
@@ -3627,7 +3407,7 @@
       <c r="G22" s="50"/>
       <c r="N22" s="14"/>
     </row>
-    <row r="23" spans="2:14" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" ht="23.25" x14ac:dyDescent="0.25">
       <c r="B23" s="89" t="s">
         <v>71</v>
       </c>
@@ -3643,7 +3423,7 @@
       <c r="L23" s="9"/>
       <c r="N23" s="14"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C25" s="97"/>
       <c r="D25" s="97"/>
       <c r="E25" s="97"/>
@@ -3652,7 +3432,7 @@
       <c r="H25" s="97"/>
       <c r="I25" s="97"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C26" s="98"/>
       <c r="D26" s="97"/>
       <c r="E26" s="97"/>
@@ -3661,7 +3441,7 @@
       <c r="H26" s="97"/>
       <c r="I26" s="97"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C27" s="97"/>
       <c r="D27" s="97"/>
       <c r="E27" s="97"/>
@@ -3670,7 +3450,7 @@
       <c r="H27" s="97"/>
       <c r="I27" s="97"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C28" s="97"/>
       <c r="D28" s="97"/>
       <c r="E28" s="97"/>
@@ -3679,7 +3459,7 @@
       <c r="H28" s="97"/>
       <c r="I28" s="97"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C29" s="97"/>
       <c r="D29" s="97"/>
       <c r="E29" s="97"/>
@@ -3688,7 +3468,7 @@
       <c r="H29" s="97"/>
       <c r="I29" s="97"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C30" s="97"/>
       <c r="D30" s="97"/>
       <c r="E30" s="97"/>
@@ -3697,7 +3477,7 @@
       <c r="H30" s="97"/>
       <c r="I30" s="97"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C31" s="97"/>
       <c r="D31" s="97"/>
       <c r="E31" s="97"/>
@@ -3706,7 +3486,7 @@
       <c r="H31" s="97"/>
       <c r="I31" s="97"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C32" s="97"/>
       <c r="D32" s="97"/>
       <c r="E32" s="97"/>
@@ -3715,7 +3495,7 @@
       <c r="H32" s="97"/>
       <c r="I32" s="97"/>
     </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C33" s="97"/>
       <c r="D33" s="97"/>
       <c r="E33" s="97"/>
@@ -3724,7 +3504,7 @@
       <c r="H33" s="97"/>
       <c r="I33" s="97"/>
     </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C34" s="97"/>
       <c r="D34" s="97"/>
       <c r="E34" s="97"/>
@@ -3733,7 +3513,7 @@
       <c r="H34" s="97"/>
       <c r="I34" s="97"/>
     </row>
-    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C35" s="97"/>
       <c r="D35" s="97"/>
       <c r="E35" s="97"/>
@@ -3742,18 +3522,18 @@
       <c r="H35" s="97"/>
       <c r="I35" s="97"/>
     </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C36" s="97"/>
-      <c r="D36" s="112" t="s">
+      <c r="D36" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="E36" s="112"/>
-      <c r="F36" s="112"/>
-      <c r="G36" s="112"/>
+      <c r="E36" s="114"/>
+      <c r="F36" s="114"/>
+      <c r="G36" s="114"/>
       <c r="H36" s="97"/>
       <c r="I36" s="97"/>
     </row>
-    <row r="37" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C37" s="97"/>
       <c r="D37" s="97"/>
       <c r="E37" s="97"/>
@@ -3762,7 +3542,7 @@
       <c r="H37" s="97"/>
       <c r="I37" s="97"/>
     </row>
-    <row r="38" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C38" s="97"/>
       <c r="D38" s="97"/>
       <c r="E38" s="97"/>
@@ -3771,7 +3551,7 @@
       <c r="H38" s="97"/>
       <c r="I38" s="97"/>
     </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C39" s="97"/>
       <c r="D39" s="97"/>
       <c r="E39" s="97"/>
@@ -3780,7 +3560,7 @@
       <c r="H39" s="97"/>
       <c r="I39" s="97"/>
     </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C40" s="97"/>
       <c r="D40" s="97"/>
       <c r="E40" s="97"/>
@@ -3789,7 +3569,7 @@
       <c r="H40" s="97"/>
       <c r="I40" s="97"/>
     </row>
-    <row r="41" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C41" s="97"/>
       <c r="D41" s="97"/>
       <c r="E41" s="97"/>
@@ -3798,7 +3578,7 @@
       <c r="H41" s="97"/>
       <c r="I41" s="97"/>
     </row>
-    <row r="42" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C42" s="97"/>
       <c r="D42" s="97"/>
       <c r="E42" s="97"/>
@@ -3807,7 +3587,7 @@
       <c r="H42" s="97"/>
       <c r="I42" s="97"/>
     </row>
-    <row r="43" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C43" s="97"/>
       <c r="D43" s="97"/>
       <c r="E43" s="97"/>
@@ -3816,7 +3596,7 @@
       <c r="H43" s="97"/>
       <c r="I43" s="97"/>
     </row>
-    <row r="44" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C44" s="97"/>
       <c r="D44" s="97"/>
       <c r="E44" s="97"/>
@@ -3825,7 +3605,7 @@
       <c r="H44" s="97"/>
       <c r="I44" s="97"/>
     </row>
-    <row r="45" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C45" s="97"/>
       <c r="D45" s="97"/>
       <c r="E45" s="97"/>
@@ -3834,7 +3614,7 @@
       <c r="H45" s="97"/>
       <c r="I45" s="97"/>
     </row>
-    <row r="46" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C46" s="97"/>
       <c r="D46" s="97"/>
       <c r="E46" s="97"/>
@@ -3843,7 +3623,7 @@
       <c r="H46" s="97"/>
       <c r="I46" s="97"/>
     </row>
-    <row r="47" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C47" s="97"/>
       <c r="D47" s="97"/>
       <c r="E47" s="97"/>
@@ -3852,7 +3632,7 @@
       <c r="H47" s="97"/>
       <c r="I47" s="97"/>
     </row>
-    <row r="48" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C48" s="97"/>
       <c r="D48" s="97"/>
       <c r="E48" s="97"/>
@@ -3861,7 +3641,7 @@
       <c r="H48" s="97"/>
       <c r="I48" s="97"/>
     </row>
-    <row r="49" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C49" s="97"/>
       <c r="D49" s="97"/>
       <c r="E49" s="97"/>
@@ -3870,7 +3650,7 @@
       <c r="H49" s="97"/>
       <c r="I49" s="97"/>
     </row>
-    <row r="50" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C50" s="97"/>
       <c r="D50" s="97"/>
       <c r="E50" s="97"/>
@@ -3879,7 +3659,7 @@
       <c r="H50" s="97"/>
       <c r="I50" s="97"/>
     </row>
-    <row r="51" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C51" s="97"/>
       <c r="D51" s="97"/>
       <c r="E51" s="97"/>
@@ -3890,11 +3670,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:F5"/>
     <mergeCell ref="D36:G36"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="D4:F4"/>
@@ -3904,6 +3679,11 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3914,41 +3694,41 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D90A4130-68CA-4E30-9267-87839E021ADD}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B1:N25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" customWidth="1"/>
-    <col min="3" max="3" width="24.109375" customWidth="1"/>
-    <col min="4" max="4" width="27.109375" customWidth="1"/>
-    <col min="5" max="5" width="23.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:14" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="8"/>
       <c r="N1" s="14"/>
     </row>
-    <row r="2" spans="2:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
+    <row r="2" spans="2:14" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
       <c r="N2" s="14"/>
     </row>
-    <row r="3" spans="2:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -3961,32 +3741,32 @@
       <c r="K3" s="1"/>
       <c r="N3" s="14"/>
     </row>
-    <row r="4" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="113" t="s">
+    <row r="4" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="114"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="108"/>
-    </row>
-    <row r="5" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="113" t="s">
+      <c r="C4" s="113"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="111"/>
+    </row>
+    <row r="5" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="108"/>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C5" s="113"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="111"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="N6" s="14"/>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N7" s="14"/>
     </row>
-    <row r="8" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="88" t="s">
         <v>54</v>
       </c>
@@ -3994,7 +3774,7 @@
       <c r="H8" s="23"/>
       <c r="N8" s="14"/>
     </row>
-    <row r="9" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="85" t="s">
         <v>35</v>
       </c>
@@ -4008,52 +3788,52 @@
       <c r="H9" s="23"/>
       <c r="N9" s="14"/>
     </row>
-    <row r="10" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="52"/>
       <c r="C10" s="53"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="105"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="101"/>
       <c r="H10" s="23"/>
       <c r="N10" s="14"/>
     </row>
-    <row r="11" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="52"/>
       <c r="C11" s="53"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="105"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="101"/>
       <c r="H11" s="23"/>
       <c r="N11" s="14"/>
     </row>
-    <row r="12" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="52"/>
       <c r="C12" s="53"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="105"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="101"/>
       <c r="H12" s="23"/>
       <c r="N12" s="14"/>
     </row>
-    <row r="13" spans="2:14" ht="21" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B13" s="52"/>
       <c r="C13" s="53"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="105"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="101"/>
       <c r="H13" s="23"/>
       <c r="N13" s="14"/>
     </row>
-    <row r="14" spans="2:14" ht="21" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B14" s="52"/>
       <c r="C14" s="53"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="105"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="101"/>
       <c r="H14" s="23"/>
       <c r="N14" s="14"/>
     </row>
-    <row r="15" spans="2:14" ht="21" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B15" s="45"/>
       <c r="C15" s="48"/>
       <c r="D15" s="49"/>
@@ -4063,7 +3843,7 @@
       <c r="H15" s="23"/>
       <c r="N15" s="14"/>
     </row>
-    <row r="16" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="88" t="s">
         <v>55</v>
       </c>
@@ -4072,7 +3852,7 @@
       <c r="H16" s="23"/>
       <c r="N16" s="14"/>
     </row>
-    <row r="17" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="85" t="s">
         <v>35</v>
       </c>
@@ -4084,31 +3864,31 @@
       <c r="H17" s="23"/>
       <c r="N17" s="14"/>
     </row>
-    <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="54"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="105"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="101"/>
       <c r="H18" s="23"/>
       <c r="N18" s="14"/>
     </row>
-    <row r="19" spans="2:14" ht="21" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B19" s="54"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="105"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="101"/>
       <c r="H19" s="23"/>
       <c r="N19" s="14"/>
     </row>
-    <row r="20" spans="2:14" ht="21" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B20" s="54"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="105"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="101"/>
       <c r="H20" s="23"/>
       <c r="N20" s="14"/>
     </row>
-    <row r="21" spans="2:14" ht="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B21" s="45"/>
       <c r="C21" s="48"/>
       <c r="D21" s="49"/>
@@ -4118,26 +3898,31 @@
       <c r="H21" s="23"/>
       <c r="N21" s="14"/>
     </row>
-    <row r="22" spans="2:14" ht="21" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B22" s="89" t="s">
         <v>43</v>
       </c>
       <c r="N22" s="14"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
       <c r="N23" s="14"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="8"/>
       <c r="N24" s="14"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="8"/>
       <c r="N25" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D12:F12"/>
@@ -4146,11 +3931,6 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4161,120 +3941,120 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58D23D63-CB16-41AC-AEAC-4444DBF1080A}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B1:J31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="113" t="s">
+    <row r="1" spans="2:10" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:10" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:10" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:10" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="122"/>
-      <c r="I5" s="122"/>
-      <c r="J5" s="123"/>
-    </row>
-    <row r="6" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="124" t="s">
+      <c r="C5" s="113"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="117"/>
+    </row>
+    <row r="6" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="118" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="124"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="123"/>
-    </row>
-    <row r="7" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="109" t="s">
+      <c r="C6" s="118"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="116"/>
+      <c r="G6" s="116"/>
+      <c r="H6" s="116"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="117"/>
+    </row>
+    <row r="7" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="108"/>
-    </row>
-    <row r="9" spans="2:10" ht="21" x14ac:dyDescent="0.3">
+      <c r="C7" s="102"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="111"/>
+    </row>
+    <row r="9" spans="2:10" ht="21" x14ac:dyDescent="0.25">
       <c r="B9" s="91" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B10" s="92" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="118"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="122"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="123"/>
+      <c r="F11" s="123"/>
+      <c r="G11" s="123"/>
+      <c r="H11" s="123"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="124"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
     </row>
-    <row r="13" spans="2:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B13" s="92" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="118"/>
-      <c r="C14" s="119"/>
-      <c r="D14" s="119"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="119"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="119"/>
-      <c r="J14" s="120"/>
-    </row>
-    <row r="16" spans="2:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="122"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="123"/>
+      <c r="E14" s="123"/>
+      <c r="F14" s="123"/>
+      <c r="G14" s="123"/>
+      <c r="H14" s="123"/>
+      <c r="I14" s="123"/>
+      <c r="J14" s="124"/>
+    </row>
+    <row r="16" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B16" s="92" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="118"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="119"/>
-      <c r="H17" s="119"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="120"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="122"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="123"/>
+      <c r="E17" s="123"/>
+      <c r="F17" s="123"/>
+      <c r="G17" s="123"/>
+      <c r="H17" s="123"/>
+      <c r="I17" s="123"/>
+      <c r="J17" s="124"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="50"/>
       <c r="C18" s="50"/>
       <c r="D18" s="50"/>
       <c r="E18" s="50"/>
     </row>
-    <row r="19" spans="2:10" ht="18" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B19" s="93" t="s">
         <v>64</v>
       </c>
@@ -4282,24 +4062,24 @@
       <c r="D19" s="50"/>
       <c r="E19" s="50"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="118"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="119"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="119"/>
-      <c r="J20" s="120"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="122"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="124"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="2:10" ht="18" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B22" s="94" t="s">
         <v>65</v>
       </c>
@@ -4307,23 +4087,23 @@
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="118"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="119"/>
-      <c r="J23" s="120"/>
-    </row>
-    <row r="25" spans="2:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="122"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="123"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="124"/>
+    </row>
+    <row r="25" spans="2:10" ht="21" x14ac:dyDescent="0.25">
       <c r="B25" s="88" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="85" t="s">
         <v>35</v>
       </c>
@@ -4331,49 +4111,43 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B27" s="56"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="117"/>
-    </row>
-    <row r="28" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="C27" s="119"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B28" s="56"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="116"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="117"/>
-    </row>
-    <row r="29" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="C28" s="119"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B29" s="56"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="104"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="104"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="105"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="99"/>
+      <c r="D29" s="100"/>
+      <c r="E29" s="100"/>
+      <c r="F29" s="100"/>
+      <c r="G29" s="100"/>
+      <c r="H29" s="101"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
     </row>
-    <row r="31" spans="2:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" ht="21" x14ac:dyDescent="0.25">
       <c r="B31" s="89" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:J7"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="B11:J11"/>
@@ -4382,6 +4156,12 @@
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="C27:H27"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4391,43 +4171,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DDBB8F-16B8-4EFB-A9D7-67A824C01276}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B1:U29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.5546875" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" customWidth="1"/>
-    <col min="4" max="4" width="31.6640625" customWidth="1"/>
-    <col min="5" max="5" width="49.109375" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.88671875" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.44140625" customWidth="1"/>
-    <col min="10" max="10" width="33.88671875" customWidth="1"/>
-    <col min="11" max="11" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="17.5546875" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="49.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.42578125" customWidth="1"/>
+    <col min="10" max="10" width="33.85546875" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="8"/>
       <c r="N1" s="14"/>
     </row>
-    <row r="2" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
+    <row r="2" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
       <c r="N2" s="14"/>
     </row>
-    <row r="3" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -4440,7 +4220,7 @@
       <c r="K3" s="1"/>
       <c r="N3" s="14"/>
     </row>
-    <row r="4" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="128" t="s">
         <v>44</v>
       </c>
@@ -4461,11 +4241,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
       <c r="N5" s="14"/>
     </row>
-    <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B6" s="88" t="s">
         <v>36</v>
       </c>
@@ -4475,68 +4255,68 @@
       <c r="G6" s="7"/>
       <c r="N6" s="14"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" s="95"/>
       <c r="C7" s="125"/>
       <c r="D7" s="126"/>
       <c r="E7" s="127"/>
       <c r="G7" s="57"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="96"/>
     </row>
-    <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B9" s="88" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="47"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" s="96"/>
       <c r="C10" s="125"/>
       <c r="D10" s="126"/>
       <c r="E10" s="127"/>
       <c r="G10" s="57"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="96"/>
     </row>
-    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B12" s="88" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B13" s="96"/>
       <c r="C13" s="125"/>
       <c r="D13" s="126"/>
       <c r="E13" s="127"/>
       <c r="G13" s="57"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="96"/>
     </row>
-    <row r="15" spans="2:21" ht="21" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B15" s="88" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" s="96"/>
       <c r="C16" s="125"/>
       <c r="D16" s="126"/>
       <c r="E16" s="127"/>
       <c r="G16" s="57"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="96"/>
     </row>
-    <row r="18" spans="2:5" ht="21" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B18" s="88" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="58" t="s">
         <v>51</v>
       </c>
@@ -4547,52 +4327,52 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C20" s="61"/>
       <c r="D20" s="62"/>
       <c r="E20" s="72"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C21" s="63"/>
       <c r="D21" s="64"/>
       <c r="E21" s="73"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C22" s="63"/>
       <c r="D22" s="64"/>
       <c r="E22" s="73"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C23" s="63"/>
       <c r="D23" s="64"/>
       <c r="E23" s="73"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C24" s="63"/>
       <c r="D24" s="64"/>
       <c r="E24" s="73"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="63"/>
       <c r="D25" s="64"/>
       <c r="E25" s="73"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C26" s="63"/>
       <c r="D26" s="64"/>
       <c r="E26" s="73"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="63"/>
       <c r="D27" s="64"/>
       <c r="E27" s="73"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C28" s="63"/>
       <c r="D28" s="64"/>
       <c r="E28" s="73"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C29" s="65"/>
       <c r="D29" s="66"/>
       <c r="E29" s="74"/>
@@ -4616,15 +4396,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83B0AAC3-C8F9-463F-BDFF-E021531C1393}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="6" max="8" width="26.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="6" max="8" width="26.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="23.25" x14ac:dyDescent="0.25">
       <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
@@ -4636,146 +4416,151 @@
       </c>
       <c r="H2" s="14"/>
     </row>
-    <row r="3" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="133" t="s">
+      <c r="C3" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="133"/>
-      <c r="F3" s="132" t="s">
+      <c r="D3" s="132"/>
+      <c r="F3" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="132"/>
-      <c r="H3" s="132"/>
-    </row>
-    <row r="4" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="133"/>
+      <c r="H3" s="133"/>
+    </row>
+    <row r="4" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="133" t="s">
+      <c r="C4" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="133"/>
+      <c r="D4" s="132"/>
       <c r="F4" s="35" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="133" t="s">
+      <c r="C5" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="133"/>
+      <c r="D5" s="132"/>
       <c r="F5" s="35" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="133" t="s">
+      <c r="C6" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="133"/>
+      <c r="D6" s="132"/>
       <c r="F6" s="36" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="133" t="s">
+      <c r="C7" s="132" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="133"/>
+      <c r="D7" s="132"/>
       <c r="F7" s="34" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="133" t="s">
+      <c r="C8" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="133"/>
-    </row>
-    <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="132"/>
+    </row>
+    <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="133" t="s">
+      <c r="C9" s="132" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="133"/>
-    </row>
-    <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="132"/>
+    </row>
+    <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="133" t="s">
+      <c r="C10" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="133"/>
-    </row>
-    <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="132"/>
+    </row>
+    <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="133" t="s">
+      <c r="C11" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="133"/>
-    </row>
-    <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="132"/>
+    </row>
+    <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="133" t="s">
+      <c r="C12" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="133"/>
-    </row>
-    <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D12" s="132"/>
+    </row>
+    <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="41"/>
       <c r="C13" s="39"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="133" t="s">
+      <c r="C14" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="133"/>
-    </row>
-    <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="132"/>
+    </row>
+    <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="40"/>
-      <c r="C15" s="133"/>
-      <c r="D15" s="133"/>
-    </row>
-    <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+    </row>
+    <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="133" t="s">
+      <c r="C16" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="133"/>
+      <c r="D16" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
@@ -4785,42 +4570,18 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
-    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5096,28 +4857,37 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
+    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5143,9 +4913,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>